--- a/NRES421_2026.xlsx
+++ b/NRES421_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GIT\NRES-470\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nevada-my.sharepoint.com/personal/kevinshoemaker_unr_edu/Documents/Documents/GitHub/NRES-470/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F1DFB12-9DEE-4F82-92E1-B1D9907BA445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{3F1DFB12-9DEE-4F82-92E1-B1D9907BA445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C51043BF-61E7-4FBB-A740-193959F67F91}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{3C139267-3727-4273-9055-F4D1C7985932}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="17472" windowHeight="10272" activeTab="2" xr2:uid="{3C139267-3727-4273-9055-F4D1C7985932}"/>
   </bookViews>
   <sheets>
     <sheet name="ExpGrowth" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="88">
   <si>
     <t>Year</t>
   </si>
@@ -149,9 +149,6 @@
   </si>
   <si>
     <t>orig</t>
-  </si>
-  <si>
-    <t>modified</t>
   </si>
   <si>
     <t>ORIG MATRIX (both errors)</t>
@@ -303,6 +300,12 @@
   <si>
     <t>POPULATION MATRIX</t>
   </si>
+  <si>
+    <t>lower</t>
+  </si>
+  <si>
+    <t>upper</t>
+  </si>
 </sst>
 </file>
 
@@ -328,7 +331,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -344,6 +347,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -507,6 +516,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14733,9 +14745,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14773,7 +14785,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -14879,7 +14891,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15021,7 +15033,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15030,16 +15042,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81565FEC-48D2-44C9-857D-35753135470A}">
   <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.26171875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="21.26171875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.41796875" customWidth="1"/>
+    <col min="9" max="9" width="19.83984375" customWidth="1"/>
+    <col min="10" max="10" width="13.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15047,7 +15059,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -15062,10 +15074,10 @@
         <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>1</v>
       </c>
@@ -15083,7 +15095,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>2</v>
       </c>
@@ -15101,7 +15113,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -15119,7 +15131,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>4</v>
       </c>
@@ -15128,7 +15140,7 @@
         <v>12.155062500000001</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>5</v>
       </c>
@@ -15137,7 +15149,7 @@
         <v>12.762815625000002</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>6</v>
       </c>
@@ -15146,7 +15158,7 @@
         <v>13.400956406250003</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -15155,16 +15167,16 @@
         <v>14.071004226562504</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>35</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>8</v>
       </c>
@@ -15184,7 +15196,7 @@
         <v>4.9999999999999989E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>9</v>
       </c>
@@ -15204,7 +15216,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>10</v>
       </c>
@@ -15224,7 +15236,7 @@
         <v>13.862943611198908</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>11</v>
       </c>
@@ -15233,7 +15245,7 @@
         <v>17.103393581163143</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>12</v>
       </c>
@@ -15242,7 +15254,7 @@
         <v>17.9585632602213</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>13</v>
       </c>
@@ -15251,7 +15263,7 @@
         <v>18.856491423232367</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>14</v>
       </c>
@@ -15260,7 +15272,7 @@
         <v>19.799315994393986</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>15</v>
       </c>
@@ -15269,7 +15281,7 @@
         <v>20.789281794113688</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>16</v>
       </c>
@@ -15278,7 +15290,7 @@
         <v>21.828745883819373</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>17</v>
       </c>
@@ -15287,7 +15299,7 @@
         <v>22.920183178010344</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>18</v>
       </c>
@@ -15296,7 +15308,7 @@
         <v>24.066192336910863</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>19</v>
       </c>
@@ -15305,7 +15317,7 @@
         <v>25.269501953756407</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>20</v>
       </c>
@@ -15314,7 +15326,7 @@
         <v>26.532977051444227</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>21</v>
       </c>
@@ -15323,7 +15335,7 @@
         <v>27.85962590401644</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>22</v>
       </c>
@@ -15332,7 +15344,7 @@
         <v>29.252607199217262</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>23</v>
       </c>
@@ -15341,7 +15353,7 @@
         <v>30.715237559178128</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>24</v>
       </c>
@@ -15350,7 +15362,7 @@
         <v>32.250999437137033</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>25</v>
       </c>
@@ -15359,7 +15371,7 @@
         <v>33.863549408993883</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>26</v>
       </c>
@@ -15368,7 +15380,7 @@
         <v>35.55672687944358</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>27</v>
       </c>
@@ -15377,7 +15389,7 @@
         <v>37.334563223415763</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>28</v>
       </c>
@@ -15386,7 +15398,7 @@
         <v>39.201291384586554</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>29</v>
       </c>
@@ -15395,7 +15407,7 @@
         <v>41.161355953815885</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>30</v>
       </c>
@@ -15404,7 +15416,7 @@
         <v>43.219423751506682</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>31</v>
       </c>
@@ -15413,7 +15425,7 @@
         <v>45.380394939082016</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>32</v>
       </c>
@@ -15422,7 +15434,7 @@
         <v>47.649414686036117</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>33</v>
       </c>
@@ -15431,7 +15443,7 @@
         <v>50.031885420337922</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>34</v>
       </c>
@@ -15440,7 +15452,7 @@
         <v>52.53347969135482</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>35</v>
       </c>
@@ -15449,7 +15461,7 @@
         <v>55.160153675922565</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>36</v>
       </c>
@@ -15458,7 +15470,7 @@
         <v>57.918161359718695</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>37</v>
       </c>
@@ -15467,7 +15479,7 @@
         <v>60.814069427704631</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>38</v>
       </c>
@@ -15476,7 +15488,7 @@
         <v>63.854772899089866</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>39</v>
       </c>
@@ -15485,7 +15497,7 @@
         <v>67.047511544044369</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>40</v>
       </c>
@@ -15494,7 +15506,7 @@
         <v>70.399887121246593</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>41</v>
       </c>
@@ -15503,7 +15515,7 @@
         <v>73.91988147730892</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>42</v>
       </c>
@@ -15512,7 +15524,7 @@
         <v>77.615875551174369</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>43</v>
       </c>
@@ -15521,7 +15533,7 @@
         <v>81.496669328733091</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>44</v>
       </c>
@@ -15530,7 +15542,7 @@
         <v>85.571502795169749</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>45</v>
       </c>
@@ -15539,7 +15551,7 @@
         <v>89.850077934928237</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>46</v>
       </c>
@@ -15548,7 +15560,7 @@
         <v>94.34258183167465</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>47</v>
       </c>
@@ -15557,7 +15569,7 @@
         <v>99.059710923258393</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>48</v>
       </c>
@@ -15566,7 +15578,7 @@
         <v>104.01269646942131</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>49</v>
       </c>
@@ -15575,7 +15587,7 @@
         <v>109.21333129289239</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>50</v>
       </c>
@@ -15594,16 +15606,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C11456-B3DA-4231-927D-921D8267BDB6}">
   <dimension ref="A1:R52"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
-    <col min="9" max="9" width="19.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.26171875" style="10" customWidth="1"/>
+    <col min="5" max="5" width="21.26171875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.41796875" customWidth="1"/>
+    <col min="9" max="9" width="19.83984375" customWidth="1"/>
+    <col min="10" max="10" width="13.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15617,7 +15629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -15632,17 +15644,17 @@
         <v>35</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <f>($F$4-$F$6*Q2)-($F$5+$F$6*Q2)</f>
+        <f t="shared" ref="R2:R33" si="0">($F$4-$F$6*Q2)-($F$5+$F$6*Q2)</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>1</v>
       </c>
@@ -15663,16 +15675,16 @@
         <v>5</v>
       </c>
       <c r="R3">
-        <f>($F$4-$F$6*Q3)-($F$5+$F$6*Q3)</f>
+        <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="10">
-        <f t="shared" ref="B4:B52" si="0">B3*(1+(($G$4-$G$6*B3)-($G$5+$G$6*B3)))</f>
+        <f t="shared" ref="B4:B52" si="1">B3*(1+(($G$4-$G$6*B3)-($G$5+$G$6*B3)))</f>
         <v>1.5568849919999999</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -15688,16 +15700,16 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <f>($F$4-$F$6*Q4)-($F$5+$F$6*Q4)</f>
+        <f t="shared" si="0"/>
         <v>0.22999999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.9412584582433701</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -15713,16 +15725,16 @@
         <v>15</v>
       </c>
       <c r="R5">
-        <f>($F$4-$F$6*Q5)-($F$5+$F$6*Q5)</f>
+        <f t="shared" si="0"/>
         <v>0.21999999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2.4190361040008095</v>
       </c>
       <c r="E6" s="7" t="s">
@@ -15738,16 +15750,16 @@
         <v>20</v>
       </c>
       <c r="R6">
-        <f>($F$4-$F$6*Q6)-($F$5+$F$6*Q6)</f>
+        <f t="shared" si="0"/>
         <v>0.20999999999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.0120916586560926</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -15757,11 +15769,11 @@
         <v>25</v>
       </c>
       <c r="R7">
-        <f>($F$4-$F$6*Q7)-($F$5+$F$6*Q7)</f>
+        <f t="shared" si="0"/>
         <v>0.19999999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>6</v>
       </c>
@@ -15773,16 +15785,16 @@
         <v>30</v>
       </c>
       <c r="R8">
-        <f>($F$4-$F$6*Q8)-($F$5+$F$6*Q8)</f>
+        <f t="shared" si="0"/>
         <v>0.18999999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4.6556319201630565</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -15792,22 +15804,22 @@
         <v>35</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q9">
         <v>35</v>
       </c>
       <c r="R9">
-        <f>($F$4-$F$6*Q9)-($F$5+$F$6*Q9)</f>
+        <f t="shared" si="0"/>
         <v>0.17999999999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.7761900830517385</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -15824,16 +15836,16 @@
         <v>40</v>
       </c>
       <c r="R10">
-        <f>($F$4-$F$6*Q10)-($F$5+$F$6*Q10)</f>
+        <f t="shared" si="0"/>
         <v>0.17000000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7.1535088600635826</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -15850,16 +15862,16 @@
         <v>45</v>
       </c>
       <c r="R11">
-        <f>($F$4-$F$6*Q11)-($F$5+$F$6*Q11)</f>
+        <f t="shared" si="0"/>
         <v>0.16000000000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.8395406970574619</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -15876,647 +15888,647 @@
         <v>50</v>
       </c>
       <c r="R12">
-        <f>($F$4-$F$6*Q12)-($F$5+$F$6*Q12)</f>
+        <f t="shared" si="0"/>
         <v>0.15000000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.893150911851958</v>
       </c>
       <c r="Q13">
         <v>55</v>
       </c>
       <c r="R13">
-        <f>($F$4-$F$6*Q13)-($F$5+$F$6*Q13)</f>
+        <f t="shared" si="0"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13.379117166238185</v>
       </c>
       <c r="Q14">
         <v>60</v>
       </c>
       <c r="R14">
-        <f>($F$4-$F$6*Q14)-($F$5+$F$6*Q14)</f>
+        <f t="shared" si="0"/>
         <v>0.13</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>16.365894905501872</v>
       </c>
       <c r="Q15">
         <v>65</v>
       </c>
       <c r="R15">
-        <f>($F$4-$F$6*Q15)-($F$5+$F$6*Q15)</f>
+        <f t="shared" si="0"/>
         <v>0.12</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19.921683599761476</v>
       </c>
       <c r="Q16">
         <v>70</v>
       </c>
       <c r="R16">
-        <f>($F$4-$F$6*Q16)-($F$5+$F$6*Q16)</f>
+        <f t="shared" si="0"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>24.10835754480383</v>
       </c>
       <c r="Q17">
         <v>75</v>
       </c>
       <c r="R17">
-        <f>($F$4-$F$6*Q17)-($F$5+$F$6*Q17)</f>
+        <f t="shared" si="0"/>
         <v>9.9999999999999978E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>28.973021123988591</v>
       </c>
       <c r="Q18">
         <v>80</v>
       </c>
       <c r="R18">
-        <f>($F$4-$F$6*Q18)-($F$5+$F$6*Q18)</f>
+        <f t="shared" si="0"/>
         <v>8.9999999999999969E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>34.537404498883561</v>
       </c>
       <c r="Q19">
         <v>85</v>
       </c>
       <c r="R19">
-        <f>($F$4-$F$6*Q19)-($F$5+$F$6*Q19)</f>
+        <f t="shared" si="0"/>
         <v>7.999999999999996E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>40.786091004565449</v>
       </c>
       <c r="Q20">
         <v>90</v>
       </c>
       <c r="R20">
-        <f>($F$4-$F$6*Q20)-($F$5+$F$6*Q20)</f>
+        <f t="shared" si="0"/>
         <v>7.0000000000000062E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>47.655603316841422</v>
       </c>
       <c r="Q21">
         <v>95</v>
       </c>
       <c r="R21">
-        <f>($F$4-$F$6*Q21)-($F$5+$F$6*Q21)</f>
+        <f t="shared" si="0"/>
         <v>6.0000000000000053E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>55.027391091067486</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <f>($F$4-$F$6*Q22)-($F$5+$F$6*Q22)</f>
+        <f t="shared" si="0"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>62.728211323255771</v>
       </c>
       <c r="Q23">
         <v>105</v>
       </c>
       <c r="R23">
-        <f>($F$4-$F$6*Q23)-($F$5+$F$6*Q23)</f>
+        <f t="shared" si="0"/>
         <v>4.0000000000000036E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>70.540607162439642</v>
       </c>
       <c r="Q24">
         <v>110</v>
       </c>
       <c r="R24">
-        <f>($F$4-$F$6*Q24)-($F$5+$F$6*Q24)</f>
+        <f t="shared" si="0"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>78.223804435358275</v>
       </c>
       <c r="Q25">
         <v>115</v>
       </c>
       <c r="R25">
-        <f>($F$4-$F$6*Q25)-($F$5+$F$6*Q25)</f>
+        <f t="shared" si="0"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>85.541828383515494</v>
       </c>
       <c r="Q26">
         <v>120</v>
       </c>
       <c r="R26">
-        <f>($F$4-$F$6*Q26)-($F$5+$F$6*Q26)</f>
+        <f t="shared" si="0"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>92.292476673004742</v>
       </c>
       <c r="Q27">
         <v>125</v>
       </c>
       <c r="R27">
-        <f>($F$4-$F$6*Q27)-($F$5+$F$6*Q27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>98.32979334038167</v>
       </c>
       <c r="Q28">
         <v>130</v>
       </c>
       <c r="R28">
-        <f>($F$4-$F$6*Q28)-($F$5+$F$6*Q28)</f>
+        <f t="shared" si="0"/>
         <v>-1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>103.57474515875275</v>
       </c>
       <c r="Q29">
         <v>135</v>
       </c>
       <c r="R29">
-        <f>($F$4-$F$6*Q29)-($F$5+$F$6*Q29)</f>
+        <f t="shared" si="0"/>
         <v>-2.0000000000000018E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>108.01297577903978</v>
       </c>
       <c r="Q30">
         <v>140</v>
       </c>
       <c r="R30">
-        <f>($F$4-$F$6*Q30)-($F$5+$F$6*Q30)</f>
+        <f t="shared" si="0"/>
         <v>-3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>111.68261385051285</v>
       </c>
       <c r="Q31">
         <v>145</v>
       </c>
       <c r="R31">
-        <f>($F$4-$F$6*Q31)-($F$5+$F$6*Q31)</f>
+        <f t="shared" si="0"/>
         <v>-4.0000000000000036E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>114.65725484017551</v>
       </c>
       <c r="Q32">
         <v>150</v>
       </c>
       <c r="R32">
-        <f>($F$4-$F$6*Q32)-($F$5+$F$6*Q32)</f>
+        <f t="shared" si="0"/>
         <v>-5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>117.02899637524949</v>
       </c>
       <c r="Q33">
         <v>155</v>
       </c>
       <c r="R33">
-        <f>($F$4-$F$6*Q33)-($F$5+$F$6*Q33)</f>
+        <f t="shared" si="0"/>
         <v>-6.0000000000000053E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>118.89467348386553</v>
       </c>
       <c r="Q34">
         <v>160</v>
       </c>
       <c r="R34">
-        <f>($F$4-$F$6*Q34)-($F$5+$F$6*Q34)</f>
+        <f t="shared" ref="R34:R52" si="2">($F$4-$F$6*Q34)-($F$5+$F$6*Q34)</f>
         <v>-7.0000000000000062E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>120.34645508916192</v>
       </c>
       <c r="Q35">
         <v>165</v>
       </c>
       <c r="R35">
-        <f>($F$4-$F$6*Q35)-($F$5+$F$6*Q35)</f>
+        <f t="shared" si="2"/>
         <v>-8.0000000000000071E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>121.46653035639706</v>
       </c>
       <c r="Q36">
         <v>170</v>
       </c>
       <c r="R36">
-        <f>($F$4-$F$6*Q36)-($F$5+$F$6*Q36)</f>
+        <f t="shared" si="2"/>
         <v>-9.000000000000008E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>122.32492695185326</v>
       </c>
       <c r="Q37">
         <v>175</v>
       </c>
       <c r="R37">
-        <f>($F$4-$F$6*Q37)-($F$5+$F$6*Q37)</f>
+        <f t="shared" si="2"/>
         <v>-0.10000000000000009</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>122.9793831822641</v>
       </c>
       <c r="Q38">
         <v>180</v>
       </c>
       <c r="R38">
-        <f>($F$4-$F$6*Q38)-($F$5+$F$6*Q38)</f>
+        <f t="shared" si="2"/>
         <v>-0.10999999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>123.47637160204984</v>
       </c>
       <c r="Q39">
         <v>185</v>
       </c>
       <c r="R39">
-        <f>($F$4-$F$6*Q39)-($F$5+$F$6*Q39)</f>
+        <f t="shared" si="2"/>
         <v>-0.12</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>123.8526358145473</v>
       </c>
       <c r="Q40">
         <v>190</v>
       </c>
       <c r="R40">
-        <f>($F$4-$F$6*Q40)-($F$5+$F$6*Q40)</f>
+        <f t="shared" si="2"/>
         <v>-0.13</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.13684397176235</v>
       </c>
       <c r="Q41">
         <v>195</v>
       </c>
       <c r="R41">
-        <f>($F$4-$F$6*Q41)-($F$5+$F$6*Q41)</f>
+        <f t="shared" si="2"/>
         <v>-0.14000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.35114290216362</v>
       </c>
       <c r="Q42">
         <v>200</v>
       </c>
       <c r="R42">
-        <f>($F$4-$F$6*Q42)-($F$5+$F$6*Q42)</f>
+        <f t="shared" si="2"/>
         <v>-0.15000000000000002</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.51251514555588</v>
       </c>
       <c r="Q43">
         <v>205</v>
       </c>
       <c r="R43">
-        <f>($F$4-$F$6*Q43)-($F$5+$F$6*Q43)</f>
+        <f t="shared" si="2"/>
         <v>-0.16000000000000003</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.63391107620026</v>
       </c>
       <c r="Q44">
         <v>210</v>
       </c>
       <c r="R44">
-        <f>($F$4-$F$6*Q44)-($F$5+$F$6*Q44)</f>
+        <f t="shared" si="2"/>
         <v>-0.16999999999999993</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.72516526494994</v>
       </c>
       <c r="Q45">
         <v>215</v>
       </c>
       <c r="R45">
-        <f>($F$4-$F$6*Q45)-($F$5+$F$6*Q45)</f>
+        <f t="shared" si="2"/>
         <v>-0.17999999999999994</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.79372288044928</v>
       </c>
       <c r="Q46">
         <v>220</v>
       </c>
       <c r="R46">
-        <f>($F$4-$F$6*Q46)-($F$5+$F$6*Q46)</f>
+        <f t="shared" si="2"/>
         <v>-0.18999999999999995</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.84520705983688</v>
       </c>
       <c r="Q47">
         <v>225</v>
       </c>
       <c r="R47">
-        <f>($F$4-$F$6*Q47)-($F$5+$F$6*Q47)</f>
+        <f t="shared" si="2"/>
         <v>-0.19999999999999996</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.88385737316899</v>
       </c>
       <c r="Q48">
         <v>230</v>
       </c>
       <c r="R48">
-        <f>($F$4-$F$6*Q48)-($F$5+$F$6*Q48)</f>
+        <f t="shared" si="2"/>
         <v>-0.20999999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.91286605165722</v>
       </c>
       <c r="Q49">
         <v>235</v>
       </c>
       <c r="R49">
-        <f>($F$4-$F$6*Q49)-($F$5+$F$6*Q49)</f>
+        <f t="shared" si="2"/>
         <v>-0.21999999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.93463435409301</v>
       </c>
       <c r="Q50">
         <v>240</v>
       </c>
       <c r="R50">
-        <f>($F$4-$F$6*Q50)-($F$5+$F$6*Q50)</f>
+        <f t="shared" si="2"/>
         <v>-0.22999999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.95096722023442</v>
       </c>
       <c r="Q51">
         <v>245</v>
       </c>
       <c r="R51">
-        <f>($F$4-$F$6*Q51)-($F$5+$F$6*Q51)</f>
+        <f t="shared" si="2"/>
         <v>-0.24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>124.96322060674882</v>
       </c>
       <c r="Q52">
         <v>250</v>
       </c>
       <c r="R52">
-        <f>($F$4-$F$6*Q52)-($F$5+$F$6*Q52)</f>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
     </row>
@@ -16529,38 +16541,38 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD7FD45B-C258-4448-AE95-CD93318BC95E}">
-  <dimension ref="A1:P82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R82"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.140625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="16" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="16" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="28.7109375" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.68359375" customWidth="1"/>
+    <col min="2" max="4" width="18.15625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="20.15625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="9.578125" customWidth="1"/>
+    <col min="8" max="8" width="11.83984375" style="16" customWidth="1"/>
+    <col min="9" max="9" width="11.578125" style="16" customWidth="1"/>
+    <col min="11" max="11" width="9.15625" customWidth="1"/>
+    <col min="14" max="14" width="28.68359375" customWidth="1"/>
+    <col min="16" max="16" width="14.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:18" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -16583,10 +16595,16 @@
         <v>35</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>1</v>
       </c>
@@ -16599,15 +16617,15 @@
         <v>50083.333333333336</v>
       </c>
       <c r="D3" s="10">
-        <f>D2*$H$15+E2*$I$15</f>
+        <f t="shared" ref="D3:D34" si="0">D2*$H$15+E2*$I$15</f>
         <v>24249.896874999999</v>
       </c>
       <c r="E3" s="10">
-        <f>D2*$H$16+E2*$I$16</f>
+        <f t="shared" ref="E3:E34" si="1">D2*$H$16+E2*$I$16</f>
         <v>48596.25</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>17</v>
@@ -16615,28 +16633,34 @@
       <c r="O3" s="14">
         <v>0.75</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P3" s="36">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q3">
+        <v>0.65</v>
+      </c>
+      <c r="R3">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="10">
-        <f t="shared" ref="B4:B67" si="0">B3*$H$5+C3*$I$5</f>
+        <f t="shared" ref="B4:B67" si="2">B3*$H$5+C3*$I$5</f>
         <v>22949.849480902776</v>
       </c>
       <c r="C4" s="10">
-        <f t="shared" ref="C4:C67" si="1">B3*$H$6+C3*$I$6</f>
+        <f t="shared" ref="C4:C67" si="3">B3*$H$6+C3*$I$6</f>
         <v>50060.234461805558</v>
       </c>
       <c r="D4" s="10">
-        <f>D3*$H$15+E3*$I$15</f>
+        <f t="shared" si="0"/>
         <v>23534.060167265623</v>
       </c>
       <c r="E4" s="10">
-        <f>D3*$H$16+E3*$I$16</f>
+        <f t="shared" si="1"/>
         <v>47230.760040468755</v>
       </c>
       <c r="H4" s="17" t="s">
@@ -16651,29 +16675,35 @@
       <c r="O4" s="12">
         <v>0.96</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="37">
         <f>0.96-P13*0</f>
         <v>0.96</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q4">
+        <v>0.93</v>
+      </c>
+      <c r="R4">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="10">
+        <f t="shared" si="2"/>
+        <v>22404.595180693359</v>
+      </c>
+      <c r="C5" s="10">
+        <f t="shared" si="3"/>
+        <v>49970.312540075232</v>
+      </c>
+      <c r="D5" s="10">
         <f t="shared" si="0"/>
-        <v>22404.595180693359</v>
-      </c>
-      <c r="C5" s="10">
+        <v>22847.770794951499</v>
+      </c>
+      <c r="E5" s="10">
         <f t="shared" si="1"/>
-        <v>49970.312540075232</v>
-      </c>
-      <c r="D5" s="10">
-        <f>D4*$H$15+E4*$I$15</f>
-        <v>22847.770794951499</v>
-      </c>
-      <c r="E5" s="10">
-        <f>D4*$H$16+E4*$I$16</f>
         <v>45902.816973839283</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -16693,28 +16723,34 @@
       <c r="O5" s="12">
         <v>0.97</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="37">
         <v>0.97</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5">
+        <v>0.9</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="10">
+        <f t="shared" si="2"/>
+        <v>22028.330330609468</v>
+      </c>
+      <c r="C6" s="10">
+        <f t="shared" si="3"/>
+        <v>49838.549636863332</v>
+      </c>
+      <c r="D6" s="10">
         <f t="shared" si="0"/>
-        <v>22028.330330609468</v>
-      </c>
-      <c r="C6" s="10">
+        <v>22187.515047729372</v>
+      </c>
+      <c r="E6" s="10">
         <f t="shared" si="1"/>
-        <v>49838.549636863332</v>
-      </c>
-      <c r="D6" s="10">
-        <f>D5*$H$15+E5*$I$15</f>
-        <v>22187.515047729372</v>
-      </c>
-      <c r="E6" s="10">
-        <f>D5*$H$16+E5*$I$16</f>
         <v>44611.623628345304</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -16734,28 +16770,34 @@
       <c r="O6" s="12">
         <v>6.5</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="37">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6">
+        <v>5.5</v>
+      </c>
+      <c r="R6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="10">
+        <f t="shared" si="2"/>
+        <v>21758.786918942846</v>
+      </c>
+      <c r="C7" s="10">
+        <f t="shared" si="3"/>
+        <v>49680.701845606251</v>
+      </c>
+      <c r="D7" s="10">
         <f t="shared" si="0"/>
-        <v>21758.786918942846</v>
-      </c>
-      <c r="C7" s="10">
+        <v>21550.644251320948</v>
+      </c>
+      <c r="E7" s="10">
         <f t="shared" si="1"/>
-        <v>49680.701845606251</v>
-      </c>
-      <c r="D7" s="10">
-        <f>D6*$H$15+E6*$I$15</f>
-        <v>21550.644251320948</v>
-      </c>
-      <c r="E7" s="10">
-        <f>D6*$H$16+E6*$I$16</f>
         <v>43356.33091709984</v>
       </c>
       <c r="N7" s="5" t="s">
@@ -16764,32 +16806,38 @@
       <c r="O7" s="12">
         <v>0.5</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="37">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q7">
+        <v>0.45</v>
+      </c>
+      <c r="R7">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" s="10">
+        <f t="shared" si="2"/>
+        <v>21556.689088952007</v>
+      </c>
+      <c r="C8" s="10">
+        <f t="shared" si="3"/>
+        <v>49506.70601502723</v>
+      </c>
+      <c r="D8" s="10">
         <f t="shared" si="0"/>
-        <v>21556.689088952007</v>
-      </c>
-      <c r="C8" s="10">
+        <v>20935.131547731587</v>
+      </c>
+      <c r="E8" s="10">
         <f t="shared" si="1"/>
-        <v>49506.70601502723</v>
-      </c>
-      <c r="D8" s="10">
-        <f>D7*$H$15+E7*$I$15</f>
-        <v>20935.131547731587</v>
-      </c>
-      <c r="E8" s="10">
-        <f>D7*$H$16+E7*$I$16</f>
         <v>42136.060545809851</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>22</v>
@@ -16797,28 +16845,34 @@
       <c r="O8" s="12">
         <v>0.35</v>
       </c>
-      <c r="P8" s="6">
+      <c r="P8" s="37">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8">
+        <v>0.1</v>
+      </c>
+      <c r="R8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" s="10">
+        <f t="shared" si="2"/>
+        <v>21397.263202902919</v>
+      </c>
+      <c r="C9" s="10">
+        <f t="shared" si="3"/>
+        <v>49322.828531838801</v>
+      </c>
+      <c r="D9" s="10">
         <f t="shared" si="0"/>
-        <v>21397.263202902919</v>
-      </c>
-      <c r="C9" s="10">
+        <v>20339.398049808282</v>
+      </c>
+      <c r="E9" s="10">
         <f t="shared" si="1"/>
-        <v>49322.828531838801</v>
-      </c>
-      <c r="D9" s="10">
-        <f>D8*$H$15+E8*$I$15</f>
-        <v>20339.398049808282</v>
-      </c>
-      <c r="E9" s="10">
-        <f>D8*$H$16+E8*$I$16</f>
         <v>40949.921011390848</v>
       </c>
       <c r="H9" s="17" t="s">
@@ -16833,28 +16887,34 @@
       <c r="O9" s="12">
         <v>0.85</v>
       </c>
-      <c r="P9" s="6">
+      <c r="P9" s="37">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9">
+        <v>0.7</v>
+      </c>
+      <c r="R9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" s="10">
+        <f t="shared" si="2"/>
+        <v>21264.882846315988</v>
+      </c>
+      <c r="C10" s="10">
+        <f t="shared" si="3"/>
+        <v>49133.020657473826</v>
+      </c>
+      <c r="D10" s="10">
         <f t="shared" si="0"/>
-        <v>21264.882846315988</v>
-      </c>
-      <c r="C10" s="10">
+        <v>19762.188553970027</v>
+      </c>
+      <c r="E10" s="10">
         <f t="shared" si="1"/>
-        <v>49133.020657473826</v>
-      </c>
-      <c r="D10" s="10">
-        <f>D9*$H$15+E9*$I$15</f>
-        <v>19762.188553970027</v>
-      </c>
-      <c r="E10" s="10">
-        <f>D9*$H$16+E9*$I$16</f>
         <v>39797.018814423143</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -16874,28 +16934,34 @@
       <c r="O10" s="12">
         <v>0.13</v>
       </c>
-      <c r="P10" s="6">
+      <c r="P10" s="37">
         <v>0.13</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10">
+        <v>0.08</v>
+      </c>
+      <c r="R10">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" s="10">
+        <f t="shared" si="2"/>
+        <v>21149.691184167525</v>
+      </c>
+      <c r="C11" s="10">
+        <f t="shared" si="3"/>
+        <v>48939.773401701197</v>
+      </c>
+      <c r="D11" s="10">
         <f t="shared" si="0"/>
-        <v>21149.691184167525</v>
-      </c>
-      <c r="C11" s="10">
+        <v>19202.482656062573</v>
+      </c>
+      <c r="E11" s="10">
         <f t="shared" si="1"/>
-        <v>48939.773401701197</v>
-      </c>
-      <c r="D11" s="10">
-        <f>D10*$H$15+E10*$I$15</f>
-        <v>19202.482656062573</v>
-      </c>
-      <c r="E11" s="10">
-        <f>D10*$H$16+E10*$I$16</f>
         <v>38676.466258858396</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -16913,30 +16979,36 @@
         <v>25</v>
       </c>
       <c r="O11" s="12">
-        <v>14</v>
-      </c>
-      <c r="P11" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P11" s="37">
+        <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>8</v>
+      </c>
+      <c r="R11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="10">
+        <f t="shared" si="2"/>
+        <v>21045.470524532149</v>
+      </c>
+      <c r="C12" s="10">
+        <f t="shared" si="3"/>
+        <v>48744.656730980438</v>
+      </c>
+      <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>21045.470524532149</v>
-      </c>
-      <c r="C12" s="10">
+        <v>18659.431159099488</v>
+      </c>
+      <c r="E12" s="10">
         <f t="shared" si="1"/>
-        <v>48744.656730980438</v>
-      </c>
-      <c r="D12" s="10">
-        <f>D11*$H$15+E11*$I$15</f>
-        <v>18659.431159099488</v>
-      </c>
-      <c r="E12" s="10">
-        <f>D11*$H$16+E11*$I$16</f>
         <v>37587.386819851148</v>
       </c>
       <c r="N12" s="5" t="s">
@@ -16945,32 +17017,38 @@
       <c r="O12" s="12">
         <v>0.01</v>
       </c>
-      <c r="P12" s="6">
+      <c r="P12" s="37">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="10">
+        <f t="shared" si="2"/>
+        <v>20948.29855371132</v>
+      </c>
+      <c r="C13" s="10">
+        <f t="shared" si="3"/>
+        <v>48548.659672118891</v>
+      </c>
+      <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>20948.29855371132</v>
-      </c>
-      <c r="C13" s="10">
+        <v>18132.310550205126</v>
+      </c>
+      <c r="E13" s="10">
         <f t="shared" si="1"/>
-        <v>48548.659672118891</v>
-      </c>
-      <c r="D13" s="10">
-        <f>D12*$H$15+E12*$I$15</f>
-        <v>18132.310550205126</v>
-      </c>
-      <c r="E13" s="10">
-        <f>D12*$H$16+E12*$I$16</f>
         <v>36528.918780201624</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N13" s="7" t="s">
         <v>27</v>
@@ -16978,28 +17056,34 @@
       <c r="O13" s="15">
         <v>2.7E-2</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P13" s="38">
         <v>2.7E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="R13">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="10">
+        <f t="shared" si="2"/>
+        <v>20855.700761495777</v>
+      </c>
+      <c r="C14" s="10">
+        <f t="shared" si="3"/>
+        <v>48352.404831376742</v>
+      </c>
+      <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>20855.700761495777</v>
-      </c>
-      <c r="C14" s="10">
+        <v>17620.490387412552</v>
+      </c>
+      <c r="E14" s="10">
         <f t="shared" si="1"/>
-        <v>48352.404831376742</v>
-      </c>
-      <c r="D14" s="10">
-        <f>D13*$H$15+E13*$I$15</f>
-        <v>17620.490387412552</v>
-      </c>
-      <c r="E14" s="10">
-        <f>D13*$H$16+E13*$I$16</f>
         <v>35500.217635615954</v>
       </c>
       <c r="H14" s="17" t="s">
@@ -17009,24 +17093,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="10">
+        <f t="shared" si="2"/>
+        <v>20766.115836522029</v>
+      </c>
+      <c r="C15" s="10">
+        <f t="shared" si="3"/>
+        <v>48156.283701579654</v>
+      </c>
+      <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>20766.115836522029</v>
-      </c>
-      <c r="C15" s="10">
+        <v>17123.409910843224</v>
+      </c>
+      <c r="E15" s="10">
         <f t="shared" si="1"/>
-        <v>48156.283701579654</v>
-      </c>
-      <c r="D15" s="10">
-        <f>D14*$H$15+E14*$I$15</f>
-        <v>17123.409910843224</v>
-      </c>
-      <c r="E15" s="10">
-        <f>D14*$H$16+E14*$I$16</f>
         <v>34500.457625931107</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -17041,24 +17125,24 @@
         <v>0.12192293749999998</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="10">
+        <f t="shared" si="2"/>
+        <v>20678.558466359576</v>
+      </c>
+      <c r="C16" s="10">
+        <f t="shared" si="3"/>
+        <v>47960.542006559968</v>
+      </c>
+      <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>20678.558466359576</v>
-      </c>
-      <c r="C16" s="10">
+        <v>16640.561245606601</v>
+      </c>
+      <c r="E16" s="10">
         <f t="shared" si="1"/>
-        <v>47960.542006559968</v>
-      </c>
-      <c r="D16" s="10">
-        <f>D15*$H$15+E15*$I$15</f>
-        <v>16640.561245606601</v>
-      </c>
-      <c r="E16" s="10">
-        <f>D15*$H$16+E15*$I$16</f>
         <v>33528.832647267474</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -17076,24 +17160,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="10">
+        <f t="shared" si="2"/>
+        <v>20592.406649902852</v>
+      </c>
+      <c r="C17" s="10">
+        <f t="shared" si="3"/>
+        <v>47765.333531827535</v>
+      </c>
+      <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>20592.406649902852</v>
-      </c>
-      <c r="C17" s="10">
+        <v>16171.477315797983</v>
+      </c>
+      <c r="E17" s="10">
         <f t="shared" si="1"/>
-        <v>47765.333531827535</v>
-      </c>
-      <c r="D17" s="10">
-        <f>D16*$H$15+E16*$I$15</f>
-        <v>16171.477315797983</v>
-      </c>
-      <c r="E17" s="10">
-        <f>D16*$H$16+E16*$I$16</f>
         <v>32584.556727084491</v>
       </c>
       <c r="N17" s="19" t="s">
@@ -17108,24 +17192,24 @@
         <v>0.93786874999999981</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" s="10">
+        <f t="shared" si="2"/>
+        <v>20507.267545439448</v>
+      </c>
+      <c r="C18" s="10">
+        <f t="shared" si="3"/>
+        <v>47570.754078046339</v>
+      </c>
+      <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>20507.267545439448</v>
-      </c>
-      <c r="C18" s="10">
+        <v>15715.72312616823</v>
+      </c>
+      <c r="E18" s="10">
         <f t="shared" si="1"/>
-        <v>47570.754078046339</v>
-      </c>
-      <c r="D18" s="10">
-        <f>D17*$H$15+E17*$I$15</f>
-        <v>15715.72312616823</v>
-      </c>
-      <c r="E18" s="10">
-        <f>D17*$H$16+E17*$I$16</f>
         <v>31666.864191982891</v>
       </c>
       <c r="N18" s="20" t="s">
@@ -17133,1363 +17217,1363 @@
       </c>
       <c r="O18" s="12">
         <f>1/(O11-1)</f>
-        <v>7.6923076923076927E-2</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P18" s="6">
         <f>1/(P11-1)</f>
         <v>0.1111111111111111</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" s="10">
+        <f t="shared" si="2"/>
+        <v>20422.892854806072</v>
+      </c>
+      <c r="C19" s="10">
+        <f t="shared" si="3"/>
+        <v>47376.862877044434</v>
+      </c>
+      <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>20422.892854806072</v>
-      </c>
-      <c r="C19" s="10">
+        <v>15272.889451767178</v>
+      </c>
+      <c r="E19" s="10">
         <f t="shared" si="1"/>
-        <v>47376.862877044434</v>
-      </c>
-      <c r="D19" s="10">
-        <f>D18*$H$15+E18*$I$15</f>
-        <v>15272.889451767178</v>
-      </c>
-      <c r="E19" s="10">
-        <f>D18*$H$16+E18*$I$16</f>
         <v>30775.009620862686</v>
       </c>
       <c r="N19" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="O19" s="15">
-        <v>1.1299999999999999E-2</v>
+      <c r="O19" s="8">
+        <v>3.1800000000000002E-2</v>
       </c>
       <c r="P19" s="8">
         <v>3.1800000000000002E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" s="10">
+        <f t="shared" si="2"/>
+        <v>20339.125452248896</v>
+      </c>
+      <c r="C20" s="10">
+        <f t="shared" si="3"/>
+        <v>47183.696099863155</v>
+      </c>
+      <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>20339.125452248896</v>
-      </c>
-      <c r="C20" s="10">
+        <v>14842.588249967073</v>
+      </c>
+      <c r="E20" s="10">
         <f t="shared" si="1"/>
-        <v>47183.696099863155</v>
-      </c>
-      <c r="D20" s="10">
-        <f>D19*$H$15+E19*$I$15</f>
-        <v>14842.588249967073</v>
-      </c>
-      <c r="E20" s="10">
-        <f>D19*$H$16+E19*$I$16</f>
         <v>29908.267649452824</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" s="10">
+        <f t="shared" si="2"/>
+        <v>20255.8657207658</v>
+      </c>
+      <c r="C21" s="10">
+        <f t="shared" si="3"/>
+        <v>46991.275376889374</v>
+      </c>
+      <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>20255.8657207658</v>
-      </c>
-      <c r="C21" s="10">
+        <v>14424.449305071097</v>
+      </c>
+      <c r="E21" s="10">
         <f t="shared" si="1"/>
-        <v>46991.275376889374</v>
-      </c>
-      <c r="D21" s="10">
-        <f>D20*$H$15+E20*$I$15</f>
-        <v>14424.449305071097</v>
-      </c>
-      <c r="E21" s="10">
-        <f>D20*$H$16+E20*$I$16</f>
         <v>29065.932673236424</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" s="10">
+        <f t="shared" si="2"/>
+        <v>20173.05031887009</v>
+      </c>
+      <c r="C22" s="10">
+        <f t="shared" si="3"/>
+        <v>46799.613171877616</v>
+      </c>
+      <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>20173.05031887009</v>
-      </c>
-      <c r="C22" s="10">
+        <v>14018.117755575588</v>
+      </c>
+      <c r="E22" s="10">
         <f t="shared" si="1"/>
-        <v>46799.613171877616</v>
-      </c>
-      <c r="D22" s="10">
-        <f>D21*$H$15+E21*$I$15</f>
-        <v>14018.117755575588</v>
-      </c>
-      <c r="E22" s="10">
-        <f>D21*$H$16+E21*$I$16</f>
         <v>28247.318482232913</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" s="10">
+        <f t="shared" si="2"/>
+        <v>20090.638787796623</v>
+      </c>
+      <c r="C23" s="10">
+        <f t="shared" si="3"/>
+        <v>46608.716171575012</v>
+      </c>
+      <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>20090.638787796623</v>
-      </c>
-      <c r="C23" s="10">
+        <v>13623.252254063091</v>
+      </c>
+      <c r="E23" s="10">
         <f t="shared" si="1"/>
-        <v>46608.716171575012</v>
-      </c>
-      <c r="D23" s="10">
-        <f>D22*$H$15+E22*$I$15</f>
-        <v>13623.252254063091</v>
-      </c>
-      <c r="E23" s="10">
-        <f>D22*$H$16+E22*$I$16</f>
         <v>27451.757851414073</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" s="10">
+        <f t="shared" si="2"/>
+        <v>20008.605104038092</v>
+      </c>
+      <c r="C24" s="10">
+        <f t="shared" si="3"/>
+        <v>46418.587423695062</v>
+      </c>
+      <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>20008.605104038092</v>
-      </c>
-      <c r="C24" s="10">
+        <v>13239.523581071004</v>
+      </c>
+      <c r="E24" s="10">
         <f t="shared" si="1"/>
-        <v>46418.587423695062</v>
-      </c>
-      <c r="D24" s="10">
-        <f>D23*$H$15+E23*$I$15</f>
-        <v>13239.523581071004</v>
-      </c>
-      <c r="E24" s="10">
-        <f>D23*$H$16+E23*$I$16</f>
         <v>26678.602103616915</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" s="10">
+        <f t="shared" si="2"/>
+        <v>19926.932351130086</v>
+      </c>
+      <c r="C25" s="10">
+        <f t="shared" si="3"/>
+        <v>46229.2276854171</v>
+      </c>
+      <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>19926.932351130086</v>
-      </c>
-      <c r="C25" s="10">
+        <v>12866.613585261362</v>
+      </c>
+      <c r="E25" s="10">
         <f t="shared" si="1"/>
-        <v>46229.2276854171</v>
-      </c>
-      <c r="D25" s="10">
-        <f>D24*$H$15+E24*$I$15</f>
-        <v>12866.613585261362</v>
-      </c>
-      <c r="E25" s="10">
-        <f>D24*$H$16+E24*$I$16</f>
         <v>25927.220656880781</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" s="10">
+        <f t="shared" si="2"/>
+        <v>19845.609358890779</v>
+      </c>
+      <c r="C26" s="10">
+        <f t="shared" si="3"/>
+        <v>46040.636273927921</v>
+      </c>
+      <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>19845.609358890779</v>
-      </c>
-      <c r="C26" s="10">
+        <v>12504.214358635121</v>
+      </c>
+      <c r="E26" s="10">
         <f t="shared" si="1"/>
-        <v>46040.636273927921</v>
-      </c>
-      <c r="D26" s="10">
-        <f>D25*$H$15+E25*$I$15</f>
-        <v>12504.214358635121</v>
-      </c>
-      <c r="E26" s="10">
-        <f>D25*$H$16+E25*$I$16</f>
         <v>25197.000564614034</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" s="10">
+        <f t="shared" si="2"/>
+        <v>19764.628583625425</v>
+      </c>
+      <c r="C27" s="10">
+        <f t="shared" si="3"/>
+        <v>45852.81160287837</v>
+      </c>
+      <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>19764.628583625425</v>
-      </c>
-      <c r="C27" s="10">
+        <v>12152.027581549793</v>
+      </c>
+      <c r="E27" s="10">
         <f t="shared" si="1"/>
-        <v>45852.81160287837</v>
-      </c>
-      <c r="D27" s="10">
-        <f>D26*$H$15+E26*$I$15</f>
-        <v>12152.027581549793</v>
-      </c>
-      <c r="E27" s="10">
-        <f>D26*$H$16+E26*$I$16</f>
         <v>24487.346054482921</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" s="10">
+        <f t="shared" si="2"/>
+        <v>19683.984771064865</v>
+      </c>
+      <c r="C28" s="10">
+        <f t="shared" si="3"/>
+        <v>45665.751520732018</v>
+      </c>
+      <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>19683.984771064865</v>
-      </c>
-      <c r="C28" s="10">
+        <v>11809.763990883976</v>
+      </c>
+      <c r="E28" s="10">
         <f t="shared" si="1"/>
-        <v>45665.751520732018</v>
-      </c>
-      <c r="D28" s="10">
-        <f>D27*$H$15+E27*$I$15</f>
-        <v>11809.763990883976</v>
-      </c>
-      <c r="E28" s="10">
-        <f>D27*$H$16+E27*$I$16</f>
         <v>23797.678070123566</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" s="10">
+        <f t="shared" si="2"/>
+        <v>19603.674113010624</v>
+      </c>
+      <c r="C29" s="10">
+        <f t="shared" si="3"/>
+        <v>45479.45352415814</v>
+      </c>
+      <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>19603.674113010624</v>
-      </c>
-      <c r="C29" s="10">
+        <v>11477.142937969194</v>
+      </c>
+      <c r="E29" s="10">
         <f t="shared" si="1"/>
-        <v>45479.45352415814</v>
-      </c>
-      <c r="D29" s="10">
-        <f>D28*$H$15+E28*$I$15</f>
-        <v>11477.142937969194</v>
-      </c>
-      <c r="E29" s="10">
-        <f>D28*$H$16+E28*$I$16</f>
         <v>23127.433818501206</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" s="10">
+        <f t="shared" si="2"/>
+        <v>19523.693715383662</v>
+      </c>
+      <c r="C30" s="10">
+        <f t="shared" si="3"/>
+        <v>45293.914892609362</v>
+      </c>
+      <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>19523.693715383662</v>
-      </c>
-      <c r="C30" s="10">
+        <v>11153.892012394837</v>
+      </c>
+      <c r="E30" s="10">
         <f t="shared" si="1"/>
-        <v>45293.914892609362</v>
-      </c>
-      <c r="D30" s="10">
-        <f>D29*$H$15+E29*$I$15</f>
-        <v>11153.892012394837</v>
-      </c>
-      <c r="E30" s="10">
-        <f>D29*$H$16+E29*$I$16</f>
         <v>22476.066324831721</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" s="10">
+        <f t="shared" si="2"/>
+        <v>19444.041262689891</v>
+      </c>
+      <c r="C31" s="10">
+        <f t="shared" si="3"/>
+        <v>45109.132773186953</v>
+      </c>
+      <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>19444.041262689891</v>
-      </c>
-      <c r="C31" s="10">
+        <v>10839.746714568822</v>
+      </c>
+      <c r="E31" s="10">
         <f t="shared" si="1"/>
-        <v>45109.132773186953</v>
-      </c>
-      <c r="D31" s="10">
-        <f>D30*$H$15+E30*$I$15</f>
-        <v>10839.746714568822</v>
-      </c>
-      <c r="E31" s="10">
-        <f>D30*$H$16+E30*$I$16</f>
         <v>21843.043996334069</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" s="10">
+        <f t="shared" si="2"/>
+        <v>19364.714806374806</v>
+      </c>
+      <c r="C32" s="10">
+        <f t="shared" si="3"/>
+        <v>44925.104234150298</v>
+      </c>
+      <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>19364.714806374806</v>
-      </c>
-      <c r="C32" s="10">
+        <v>10534.450164758939</v>
+      </c>
+      <c r="E32" s="10">
         <f t="shared" si="1"/>
-        <v>44925.104234150298</v>
-      </c>
-      <c r="D32" s="10">
-        <f>D31*$H$15+E31*$I$15</f>
-        <v>10534.450164758939</v>
-      </c>
-      <c r="E32" s="10">
-        <f>D31*$H$16+E31*$I$16</f>
         <v>21227.85019562317</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" s="10">
+        <f t="shared" si="2"/>
+        <v>19285.712631320835</v>
+      </c>
+      <c r="C33" s="10">
+        <f t="shared" si="3"/>
+        <v>44741.826298648848</v>
+      </c>
+      <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>19285.712631320835</v>
-      </c>
-      <c r="C33" s="10">
+        <v>10237.752839800029</v>
+      </c>
+      <c r="E33" s="10">
         <f t="shared" si="1"/>
-        <v>44741.826298648848</v>
-      </c>
-      <c r="D33" s="10">
-        <f>D32*$H$15+E32*$I$15</f>
-        <v>10237.752839800029</v>
-      </c>
-      <c r="E33" s="10">
-        <f>D32*$H$16+E32*$I$16</f>
         <v>20629.982824227744</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" s="10">
+        <f t="shared" si="2"/>
+        <v>19207.033171632887</v>
+      </c>
+      <c r="C34" s="10">
+        <f t="shared" si="3"/>
+        <v>44559.295965979632</v>
+      </c>
+      <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>19207.033171632887</v>
-      </c>
-      <c r="C34" s="10">
+        <v>9949.4123311251824</v>
+      </c>
+      <c r="E34" s="10">
         <f t="shared" si="1"/>
-        <v>44559.295965979632</v>
-      </c>
-      <c r="D34" s="10">
-        <f>D33*$H$15+E33*$I$15</f>
-        <v>9949.4123311251824</v>
-      </c>
-      <c r="E34" s="10">
-        <f>D33*$H$16+E33*$I$16</f>
         <v>20048.953916487862</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>19128.674957512318</v>
       </c>
       <c r="C35" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>44377.510224976519</v>
       </c>
       <c r="D35" s="10">
-        <f>D34*$H$15+E34*$I$15</f>
+        <f t="shared" ref="D35:D66" si="4">D34*$H$15+E34*$I$15</f>
         <v>9669.1931195468806</v>
       </c>
       <c r="E35" s="10">
-        <f>D34*$H$16+E34*$I$16</f>
+        <f t="shared" ref="E35:E66" si="5">D34*$H$16+E34*$I$16</f>
         <v>19484.289243925683</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>19050.636581739833</v>
       </c>
       <c r="C36" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>44196.466062436819</v>
       </c>
       <c r="D36" s="10">
-        <f>D35*$H$15+E35*$I$15</f>
+        <f t="shared" si="4"/>
         <v>9396.8663634780387</v>
       </c>
       <c r="E36" s="10">
-        <f>D35*$H$16+E35*$I$16</f>
+        <f t="shared" si="5"/>
         <v>18935.527930069846</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18972.916678526646</v>
       </c>
       <c r="C37" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>44016.160468417671</v>
       </c>
       <c r="D37" s="10">
-        <f>D36*$H$15+E36*$I$15</f>
+        <f t="shared" si="4"/>
         <v>9132.2096981869872</v>
       </c>
       <c r="E37" s="10">
-        <f>D36*$H$16+E36*$I$16</f>
+        <f t="shared" si="5"/>
         <v>18402.222075636004</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18895.513910166974</v>
       </c>
       <c r="C38" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>43836.590439558182</v>
       </c>
       <c r="D38" s="10">
-        <f>D37*$H$15+E37*$I$15</f>
+        <f t="shared" si="4"/>
         <v>8875.0070443273689</v>
       </c>
       <c r="E38" s="10">
-        <f>D37*$H$16+E37*$I$16</f>
+        <f t="shared" si="5"/>
         <v>17883.936393912321</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18818.426958611162</v>
       </c>
       <c r="C39" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>43657.752981156438</v>
       </c>
       <c r="D39" s="10">
-        <f>D38*$H$15+E38*$I$15</f>
+        <f t="shared" si="4"/>
         <v>8625.0484244472646</v>
       </c>
       <c r="E39" s="10">
-        <f>D38*$H$16+E38*$I$16</f>
+        <f t="shared" si="5"/>
         <v>17380.247856163034</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18741.654520142543</v>
       </c>
       <c r="C40" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>43479.645108461111</v>
       </c>
       <c r="D40" s="10">
-        <f>D39*$H$15+E39*$I$15</f>
+        <f t="shared" si="4"/>
         <v>8382.1297865138549</v>
       </c>
       <c r="E40" s="10">
-        <f>D39*$H$16+E39*$I$16</f>
+        <f t="shared" si="5"/>
         <v>16890.74534683958</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18665.195302012002</v>
       </c>
       <c r="C41" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>43302.263847467875</v>
       </c>
       <c r="D41" s="10">
-        <f>D40*$H$15+E40*$I$15</f>
+        <f t="shared" si="4"/>
         <v>8146.0528337281739</v>
       </c>
       <c r="E41" s="10">
-        <f>D40*$H$16+E40*$I$16</f>
+        <f t="shared" si="5"/>
         <v>16415.029328374352</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18589.04802030736</v>
       </c>
       <c r="C42" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>43125.606235403495</v>
       </c>
       <c r="D42" s="10">
-        <f>D41*$H$15+E41*$I$15</f>
+        <f t="shared" si="4"/>
         <v>7916.6248600757663</v>
       </c>
       <c r="E42" s="10">
-        <f>D41*$H$16+E41*$I$16</f>
+        <f t="shared" si="5"/>
         <v>15952.711515323794</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18513.211398601685</v>
       </c>
       <c r="C43" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42949.669321012967</v>
       </c>
       <c r="D43" s="10">
-        <f>D42*$H$15+E42*$I$15</f>
+        <f t="shared" si="4"/>
         <v>7693.6585911823704</v>
       </c>
       <c r="E43" s="10">
-        <f>D42*$H$16+E42*$I$16</f>
+        <f t="shared" si="5"/>
         <v>15503.41455762365</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18437.684167092913</v>
       </c>
       <c r="C44" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42774.450164722584</v>
       </c>
       <c r="D44" s="10">
-        <f>D43*$H$15+E43*$I$15</f>
+        <f t="shared" si="4"/>
         <v>7476.9720301328161</v>
       </c>
       <c r="E44" s="10">
-        <f>D43*$H$16+E43*$I$16</f>
+        <f t="shared" si="5"/>
         <v>15066.771732718402</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18362.465062053398</v>
       </c>
       <c r="C45" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42599.945838724758</v>
       </c>
       <c r="D45" s="10">
-        <f>D44*$H$15+E44*$I$15</f>
+        <f t="shared" si="4"/>
         <v>7266.3883079759362</v>
       </c>
       <c r="E45" s="10">
-        <f>D44*$H$16+E44*$I$16</f>
+        <f t="shared" si="5"/>
         <v>14642.426646328333</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18287.552825474981</v>
       </c>
       <c r="C46" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42426.153427013545</v>
       </c>
       <c r="D46" s="10">
-        <f>D45*$H$15+E45*$I$15</f>
+        <f t="shared" si="4"/>
         <v>7061.7355386853487</v>
       </c>
       <c r="E46" s="10">
-        <f>D45*$H$16+E45*$I$16</f>
+        <f t="shared" si="5"/>
         <v>14230.032941620426</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18212.946204837441</v>
       </c>
       <c r="C47" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42253.07002538925</v>
       </c>
       <c r="D47" s="10">
-        <f>D46*$H$15+E46*$I$15</f>
+        <f t="shared" si="4"/>
         <v>6862.8466783804943</v>
       </c>
       <c r="E47" s="10">
-        <f>D46*$H$16+E46*$I$16</f>
+        <f t="shared" si="5"/>
         <v>13829.254016553254</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18138.643952954735</v>
       </c>
       <c r="C48" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>42080.692741443469</v>
       </c>
       <c r="D48" s="10">
-        <f>D47*$H$15+E47*$I$15</f>
+        <f t="shared" si="4"/>
         <v>6669.559388637841</v>
       </c>
       <c r="E48" s="10">
-        <f>D47*$H$16+E47*$I$16</f>
+        <f t="shared" si="5"/>
         <v>13439.762749170499</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18064.644827870408</v>
       </c>
       <c r="C49" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>41909.018694531958</v>
       </c>
       <c r="D49" s="10">
-        <f>D48*$H$15+E48*$I$15</f>
+        <f t="shared" si="4"/>
         <v>6481.7159037413112</v>
       </c>
       <c r="E49" s="10">
-        <f>D48*$H$16+E48*$I$16</f>
+        <f t="shared" si="5"/>
         <v>13061.241230622692</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17990.947592783996</v>
       </c>
       <c r="C50" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>41738.045015739881</v>
       </c>
       <c r="D50" s="10">
-        <f>D49*$H$15+E49*$I$15</f>
+        <f t="shared" si="4"/>
         <v>6299.1629017353862</v>
       </c>
       <c r="E50" s="10">
-        <f>D49*$H$16+E49*$I$16</f>
+        <f t="shared" si="5"/>
         <v>12693.380505702016</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17917.551015997036</v>
       </c>
       <c r="C51" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>41567.768847842279</v>
       </c>
       <c r="D51" s="10">
-        <f>D50*$H$15+E50*$I$15</f>
+        <f t="shared" si="4"/>
         <v>6121.7513791555757</v>
       </c>
       <c r="E51" s="10">
-        <f>D50*$H$16+E50*$I$16</f>
+        <f t="shared" si="5"/>
         <v>12335.880320680324</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17844.453870871457</v>
       </c>
       <c r="C52" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>41398.187345261671</v>
       </c>
       <c r="D52" s="10">
-        <f>D51*$H$15+E51*$I$15</f>
+        <f t="shared" si="4"/>
         <v>5949.3365293196075</v>
       </c>
       <c r="E52" s="10">
-        <f>D51*$H$16+E51*$I$16</f>
+        <f t="shared" si="5"/>
         <v>11988.448878245972</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17771.654935795832</v>
       </c>
       <c r="C53" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>41229.297674023823</v>
       </c>
       <c r="D53" s="10">
-        <f>D52*$H$15+E52*$I$15</f>
+        <f t="shared" si="4"/>
         <v>5781.7776240697622</v>
       </c>
       <c r="E53" s="10">
-        <f>D52*$H$16+E52*$I$16</f>
+        <f t="shared" si="5"/>
         <v>11650.802599340406</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17699.152994156597</v>
       </c>
       <c r="C54" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>41061.097011712525</v>
       </c>
       <c r="D54" s="10">
-        <f>D53*$H$15+E53*$I$15</f>
+        <f t="shared" si="4"/>
         <v>5618.9378988624749</v>
       </c>
       <c r="E54" s="10">
-        <f>D53*$H$16+E53*$I$16</f>
+        <f t="shared" si="5"/>
         <v>11322.665891700854</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17626.946834312443</v>
       </c>
       <c r="C55" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>40893.582547423735</v>
       </c>
       <c r="D55" s="10">
-        <f>D54*$H$15+E54*$I$15</f>
+        <f t="shared" si="4"/>
         <v>5460.6844411062102</v>
       </c>
       <c r="E55" s="10">
-        <f>D54*$H$16+E54*$I$16</f>
+        <f t="shared" si="5"/>
         <v>11003.770924920689</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>54</v>
       </c>
       <c r="B56" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17555.035249570738</v>
       </c>
       <c r="C56" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>40726.751481719482</v>
       </c>
       <c r="D56" s="10">
-        <f>D55*$H$15+E55*$I$15</f>
+        <f t="shared" si="4"/>
         <v>5306.8880816526962</v>
       </c>
       <c r="E56" s="10">
-        <f>D55*$H$16+E55*$I$16</f>
+        <f t="shared" si="5"/>
         <v>10693.857411844243</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>55</v>
       </c>
       <c r="B57" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17483.417038165262</v>
       </c>
       <c r="C57" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>40560.6010265816</v>
       </c>
       <c r="D57" s="10">
-        <f>D56*$H$15+E56*$I$15</f>
+        <f t="shared" si="4"/>
         <v>5157.4232893503022</v>
       </c>
       <c r="E57" s="10">
-        <f>D56*$H$16+E56*$I$16</f>
+        <f t="shared" si="5"/>
         <v>10392.67239611789</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>56</v>
       </c>
       <c r="B58" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17412.091003234818</v>
       </c>
       <c r="C58" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>40395.128405365445</v>
       </c>
       <c r="D58" s="10">
-        <f>D57*$H$15+E57*$I$15</f>
+        <f t="shared" si="4"/>
         <v>5012.1680685715783</v>
       </c>
       <c r="E58" s="10">
-        <f>D57*$H$16+E57*$I$16</f>
+        <f t="shared" si="5"/>
         <v>10099.97004572418</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>57</v>
       </c>
       <c r="B59" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17341.055952802366</v>
       </c>
       <c r="C59" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>40230.330852753723</v>
       </c>
       <c r="D59" s="10">
-        <f>D58*$H$15+E58*$I$15</f>
+        <f t="shared" si="4"/>
         <v>4871.0038596299528</v>
       </c>
       <c r="E59" s="10">
-        <f>D58*$H$16+E58*$I$16</f>
+        <f t="shared" si="5"/>
         <v>9815.5114523306438</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>58</v>
       </c>
       <c r="B60" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17270.310699754598</v>
       </c>
       <c r="C60" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>40066.20561471043</v>
       </c>
       <c r="D60" s="10">
-        <f>D59*$H$15+E59*$I$15</f>
+        <f t="shared" si="4"/>
         <v>4733.8154420033334</v>
       </c>
       <c r="E60" s="10">
-        <f>D59*$H$16+E59*$I$16</f>
+        <f t="shared" si="5"/>
         <v>9539.0644362895928</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>59</v>
       </c>
       <c r="B61" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17199.854061821763</v>
       </c>
       <c r="C61" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>39902.749948434895</v>
       </c>
       <c r="D61" s="10">
-        <f>D60*$H$15+E60*$I$15</f>
+        <f t="shared" si="4"/>
         <v>4600.4908402849287</v>
       </c>
       <c r="E61" s="10">
-        <f>D60*$H$16+E60*$I$16</f>
+        <f t="shared" si="5"/>
         <v>9270.4033571297878</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17129.684861557696</v>
       </c>
       <c r="C62" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>39739.961122315981</v>
       </c>
       <c r="D62" s="10">
-        <f>D61*$H$15+E61*$I$15</f>
+        <f t="shared" si="4"/>
         <v>4470.921232784026</v>
       </c>
       <c r="E62" s="10">
-        <f>D61*$H$16+E61*$I$16</f>
+        <f t="shared" si="5"/>
         <v>9009.30892938539</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17059.801926320011</v>
       </c>
       <c r="C63" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>39577.836415886486</v>
       </c>
       <c r="D63" s="10">
-        <f>D62*$H$15+E62*$I$15</f>
+        <f t="shared" si="4"/>
         <v>4345.0008627017669</v>
       </c>
       <c r="E63" s="10">
-        <f>D62*$H$16+E62*$I$16</f>
+        <f t="shared" si="5"/>
         <v>8755.5680436118728</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>62</v>
       </c>
       <c r="B64" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>16990.204088250423</v>
       </c>
       <c r="C64" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>39416.373119777694</v>
       </c>
       <c r="D64" s="10">
-        <f>D63*$H$15+E63*$I$15</f>
+        <f t="shared" si="4"/>
         <v>4222.6269518091749</v>
       </c>
       <c r="E64" s="10">
-        <f>D63*$H$16+E63*$I$16</f>
+        <f t="shared" si="5"/>
         <v>8508.9735924428333</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>63</v>
       </c>
       <c r="B65" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>16920.890184255171</v>
       </c>
       <c r="C65" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>39255.568535674116</v>
       </c>
       <c r="D65" s="10">
-        <f>D64*$H$15+E64*$I$15</f>
+        <f t="shared" si="4"/>
         <v>4103.6996165567907</v>
       </c>
       <c r="E65" s="10">
-        <f>D64*$H$16+E64*$I$16</f>
+        <f t="shared" si="5"/>
         <v>8269.3243015457683</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>64</v>
       </c>
       <c r="B66" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>16851.859055985558</v>
       </c>
       <c r="C66" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>39095.419976268415</v>
       </c>
       <c r="D66" s="10">
-        <f>D65*$H$15+E65*$I$15</f>
+        <f t="shared" si="4"/>
         <v>3988.1217865473091</v>
       </c>
       <c r="E66" s="10">
-        <f>D65*$H$16+E65*$I$16</f>
+        <f t="shared" si="5"/>
         <v>8036.424565338817</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>65</v>
       </c>
       <c r="B67" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>16783.109549818564</v>
       </c>
       <c r="C67" s="10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>38935.924765216478</v>
       </c>
       <c r="D67" s="10">
-        <f>D66*$H$15+E66*$I$15</f>
+        <f t="shared" ref="D67:D82" si="6">D66*$H$15+E66*$I$15</f>
         <v>3875.7991253045975</v>
       </c>
       <c r="E67" s="10">
-        <f>D66*$H$16+E66*$I$16</f>
+        <f t="shared" ref="E67:E82" si="7">D66*$H$16+E66*$I$16</f>
         <v>7810.0842873344172</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>66</v>
       </c>
       <c r="B68" s="10">
-        <f t="shared" ref="B68:B82" si="2">B67*$H$5+C67*$I$5</f>
+        <f t="shared" ref="B68:B82" si="8">B67*$H$5+C67*$I$5</f>
         <v>16714.640516837564</v>
       </c>
       <c r="C68" s="10">
-        <f t="shared" ref="C68:C82" si="3">B67*$H$6+C67*$I$6</f>
+        <f t="shared" ref="C68:C82" si="9">B67*$H$6+C67*$I$6</f>
         <v>38777.080237092698</v>
       </c>
       <c r="D68" s="10">
-        <f>D67*$H$15+E67*$I$15</f>
+        <f t="shared" si="6"/>
         <v>3766.6399532743394</v>
       </c>
       <c r="E68" s="10">
-        <f>D67*$H$16+E67*$I$16</f>
+        <f t="shared" si="7"/>
         <v>7590.1187249795548</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>67</v>
       </c>
       <c r="B69" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16646.450812813102</v>
       </c>
       <c r="C69" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>38618.883737345452</v>
       </c>
       <c r="D69" s="10">
-        <f>D68*$H$15+E68*$I$15</f>
+        <f t="shared" si="6"/>
         <v>3660.5551729934232</v>
       </c>
       <c r="E69" s="10">
-        <f>D68*$H$16+E68*$I$16</f>
+        <f t="shared" si="7"/>
         <v>7376.3483388659652</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>68</v>
       </c>
       <c r="B70" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16578.539298183779</v>
       </c>
       <c r="C70" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>38461.332622252725</v>
       </c>
       <c r="D70" s="10">
-        <f>D69*$H$15+E69*$I$15</f>
+        <f t="shared" si="6"/>
         <v>3557.458196366958</v>
       </c>
       <c r="E70" s="10">
-        <f>D69*$H$16+E69*$I$16</f>
+        <f t="shared" si="7"/>
         <v>7168.5986461872189</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="B71" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16510.904838037204</v>
       </c>
       <c r="C71" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>38304.424258877923</v>
       </c>
       <c r="D71" s="10">
-        <f>D70*$H$15+E70*$I$15</f>
+        <f t="shared" si="6"/>
         <v>3457.2648739935353</v>
       </c>
       <c r="E71" s="10">
-        <f>D70*$H$16+E70*$I$16</f>
+        <f t="shared" si="7"/>
         <v>6966.7000783230815</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>70</v>
       </c>
       <c r="B72" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16443.546302091017</v>
       </c>
       <c r="C72" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>38148.156025025906</v>
       </c>
       <c r="D72" s="10">
-        <f>D71*$H$15+E71*$I$15</f>
+        <f t="shared" si="6"/>
         <v>3359.8934264810355</v>
       </c>
       <c r="E72" s="10">
-        <f>D71*$H$16+E71*$I$16</f>
+        <f t="shared" si="7"/>
         <v>6770.4878424349035</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>71</v>
       </c>
       <c r="B73" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16376.462564674011</v>
       </c>
       <c r="C73" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>37992.525309199125</v>
       </c>
       <c r="D73" s="10">
-        <f>D72*$H$15+E72*$I$15</f>
+        <f t="shared" si="6"/>
         <v>3265.2643776969044</v>
       </c>
       <c r="E73" s="10">
-        <f>D72*$H$16+E72*$I$16</f>
+        <f t="shared" si="7"/>
         <v>6579.8017869590803</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>72</v>
       </c>
       <c r="B74" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16309.652504707308</v>
       </c>
       <c r="C74" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>37837.529510553992</v>
       </c>
       <c r="D74" s="10">
-        <f>D73*$H$15+E73*$I$15</f>
+        <f t="shared" si="6"/>
         <v>3173.3004898984072</v>
       </c>
       <c r="E74" s="10">
-        <f>D73*$H$16+E73*$I$16</f>
+        <f t="shared" si="7"/>
         <v>6394.4862708887877</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>73</v>
       </c>
       <c r="B75" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16243.115005685631</v>
       </c>
       <c r="C75" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>37683.166038857446</v>
       </c>
       <c r="D75" s="10">
-        <f>D74*$H$15+E74*$I$15</f>
+        <f t="shared" si="6"/>
         <v>3083.9267006899099</v>
       </c>
       <c r="E75" s="10">
-        <f>D74*$H$16+E74*$I$16</f>
+        <f t="shared" si="7"/>
         <v>6214.3900367373126</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>74</v>
       </c>
       <c r="B76" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16176.848955658639</v>
       </c>
       <c r="C76" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>37529.43231444362</v>
       </c>
       <c r="D76" s="10">
-        <f>D75*$H$15+E75*$I$15</f>
+        <f t="shared" si="6"/>
         <v>2997.0700617557241</v>
       </c>
       <c r="E76" s="10">
-        <f>D75*$H$16+E75*$I$16</f>
+        <f t="shared" si="7"/>
         <v>6039.3660870792746</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>75</v>
       </c>
       <c r="B77" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16110.853247212355</v>
       </c>
       <c r="C77" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>37376.325768170762</v>
       </c>
       <c r="D77" s="10">
-        <f>D76*$H$15+E76*$I$15</f>
+        <f t="shared" si="6"/>
         <v>2912.6596793185045</v>
       </c>
       <c r="E77" s="10">
-        <f>D76*$H$16+E76*$I$16</f>
+        <f t="shared" si="7"/>
         <v>5869.2715645689777</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>76</v>
       </c>
       <c r="B78" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>16045.126777450641</v>
       </c>
       <c r="C78" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>37223.843841378293</v>
       </c>
       <c r="D78" s="10">
-        <f>D77*$H$15+E77*$I$15</f>
+        <f t="shared" si="6"/>
         <v>2830.6266562746023</v>
       </c>
       <c r="E78" s="10">
-        <f>D77*$H$16+E77*$I$16</f>
+        <f t="shared" si="7"/>
         <v>5703.9676353379655</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>77</v>
       </c>
       <c r="B79" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>15979.668447976785</v>
       </c>
       <c r="C79" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>37071.983985844046</v>
       </c>
       <c r="D79" s="10">
-        <f>D78*$H$15+E78*$I$15</f>
+        <f t="shared" si="6"/>
         <v>2750.9040359591359</v>
       </c>
       <c r="E79" s="10">
-        <f>D78*$H$16+E78*$I$16</f>
+        <f t="shared" si="7"/>
         <v>5543.3193756765959</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>78</v>
       </c>
       <c r="B80" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>15914.477164875134</v>
       </c>
       <c r="C80" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>36920.743663741683</v>
       </c>
       <c r="D80" s="10">
-        <f>D79*$H$15+E79*$I$15</f>
+        <f t="shared" si="6"/>
         <v>2673.4267474948829</v>
       </c>
       <c r="E80" s="10">
-        <f>D79*$H$16+E79*$I$16</f>
+        <f t="shared" si="7"/>
         <v>5387.195661907157</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>79</v>
       </c>
       <c r="B81" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>15849.55183869282</v>
       </c>
       <c r="C81" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>36770.120347598277</v>
       </c>
       <c r="D81" s="10">
-        <f>D80*$H$15+E80*$I$15</f>
+        <f t="shared" si="6"/>
         <v>2598.1315526803864</v>
       </c>
       <c r="E81" s="10">
-        <f>D80*$H$16+E80*$I$16</f>
+        <f t="shared" si="7"/>
         <v>5235.4690633586233</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>80</v>
       </c>
       <c r="B82" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>15784.891384421548</v>
       </c>
       <c r="C82" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v>36620.111520252081</v>
       </c>
       <c r="D82" s="10">
-        <f>D81*$H$15+E81*$I$15</f>
+        <f t="shared" si="6"/>
         <v>2524.9569943739193</v>
       </c>
       <c r="E82" s="10">
-        <f>D81*$H$16+E81*$I$16</f>
+        <f t="shared" si="7"/>
         <v>5088.0157383557062</v>
       </c>
     </row>
@@ -18503,39 +18587,39 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39DF746A-F989-4347-AA9A-90C3A5A1566F}">
   <dimension ref="A1:S82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="3" width="13.7109375" style="10" customWidth="1"/>
-    <col min="4" max="5" width="18.140625" style="10" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" style="16" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" style="16" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="28.7109375" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.68359375" customWidth="1"/>
+    <col min="2" max="3" width="13.68359375" style="10" customWidth="1"/>
+    <col min="4" max="5" width="18.15625" style="10" customWidth="1"/>
+    <col min="7" max="7" width="9.578125" customWidth="1"/>
+    <col min="8" max="8" width="11.83984375" style="16" customWidth="1"/>
+    <col min="9" max="9" width="11.578125" style="16" customWidth="1"/>
+    <col min="11" max="11" width="9.15625" customWidth="1"/>
+    <col min="14" max="14" width="28.68359375" customWidth="1"/>
+    <col min="15" max="15" width="14.15625" customWidth="1"/>
+    <col min="16" max="16" width="14.83984375" customWidth="1"/>
     <col min="18" max="18" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -18558,10 +18642,10 @@
         <v>35</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -18585,7 +18669,7 @@
         <v>28</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O3" s="14">
         <v>0.75</v>
@@ -18594,10 +18678,10 @@
         <v>0.75</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>2</v>
       </c>
@@ -18624,7 +18708,7 @@
         <v>30</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O4" s="25">
         <f>1/(1+EXP(-1*(2.259+ O12*LOG(O16) )   ))</f>
@@ -18635,13 +18719,13 @@
         <v>0.78</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S4" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>3</v>
       </c>
@@ -18682,13 +18766,13 @@
         <v>1</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S5" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>4</v>
       </c>
@@ -18729,13 +18813,13 @@
         <v>4</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S6" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -18765,13 +18849,13 @@
         <v>0.5</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S7" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
         <v>6</v>
       </c>
@@ -18792,7 +18876,7 @@
         <v>39345.312647952</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>22</v>
@@ -18804,7 +18888,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
         <v>7</v>
       </c>
@@ -18840,7 +18924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -18881,10 +18965,10 @@
         <v>0.25</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>9</v>
       </c>
@@ -18925,13 +19009,13 @@
         <v>2</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="S11" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
         <v>10</v>
       </c>
@@ -18952,20 +19036,20 @@
         <v>39992.165621163505</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O12" s="12">
         <v>0.38</v>
       </c>
       <c r="P12" s="29"/>
       <c r="R12" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S12" s="6">
         <v>0.1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A13">
         <v>11</v>
       </c>
@@ -18986,20 +19070,20 @@
         <v>40155.521163509882</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O13" s="28"/>
       <c r="P13" s="8">
         <v>0.10299999999999999</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S13" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A14">
         <v>12</v>
       </c>
@@ -19022,13 +19106,13 @@
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
       <c r="R14" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S14" s="8">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>13</v>
       </c>
@@ -19052,10 +19136,10 @@
       <c r="H15" s="25"/>
       <c r="I15" s="25"/>
       <c r="N15" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>14</v>
       </c>
@@ -19079,14 +19163,14 @@
       <c r="H16" s="25"/>
       <c r="I16" s="25"/>
       <c r="N16" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O16" s="26">
         <v>8</v>
       </c>
       <c r="P16" s="27"/>
     </row>
-    <row r="17" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A17">
         <v>15</v>
       </c>
@@ -19107,14 +19191,14 @@
         <v>40815.642551284953</v>
       </c>
       <c r="N17" s="21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O17" s="28"/>
       <c r="P17" s="24">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>16</v>
       </c>
@@ -19135,7 +19219,7 @@
         <v>40982.361582409096</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>17</v>
       </c>
@@ -19162,10 +19246,10 @@
         <v>35</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>18</v>
       </c>
@@ -19197,7 +19281,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>19</v>
       </c>
@@ -19229,7 +19313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A22">
         <v>20</v>
       </c>
@@ -19259,7 +19343,7 @@
         <v>1.0113000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>21</v>
       </c>
@@ -19280,7 +19364,7 @@
         <v>41826.227462337862</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>22</v>
       </c>
@@ -19301,7 +19385,7 @@
         <v>41997.074414287577</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>23</v>
       </c>
@@ -19322,7 +19406,7 @@
         <v>42168.619222170331</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>24</v>
       </c>
@@ -19343,7 +19427,7 @@
         <v>42340.864736507559</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>25</v>
       </c>
@@ -19364,7 +19448,7 @@
         <v>42513.813819464216</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
         <v>26</v>
       </c>
@@ -19385,7 +19469,7 @@
         <v>42687.469344896286</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>27</v>
       </c>
@@ -19406,7 +19490,7 @@
         <v>42861.834198398552</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>28</v>
       </c>
@@ -19427,7 +19511,7 @@
         <v>43036.911277352534</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>29</v>
       </c>
@@ -19448,7 +19532,7 @@
         <v>43212.703490974651</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>30</v>
       </c>
@@ -19469,7 +19553,7 @@
         <v>43389.213760364553</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>31</v>
       </c>
@@ -19490,7 +19574,7 @@
         <v>43566.445018553648</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>32</v>
       </c>
@@ -19511,7 +19595,7 @@
         <v>43744.400210553868</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>33</v>
       </c>
@@ -19532,7 +19616,7 @@
         <v>43923.082293406587</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>34</v>
       </c>
@@ -19553,7 +19637,7 @@
         <v>44102.494236231752</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>35</v>
       </c>
@@ -19574,7 +19658,7 @@
         <v>44282.639020277245</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>36</v>
       </c>
@@ -19595,7 +19679,7 @@
         <v>44463.519638968399</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>37</v>
       </c>
@@ -19616,7 +19700,7 @@
         <v>44645.139097957726</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>38</v>
       </c>
@@ -19637,7 +19721,7 @@
         <v>44827.500415174916</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>39</v>
       </c>
@@ -19658,7 +19742,7 @@
         <v>45010.606620876919</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>40</v>
       </c>
@@ -19679,7 +19763,7 @@
         <v>45194.460757698354</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>41</v>
       </c>
@@ -19700,7 +19784,7 @@
         <v>45379.065880702023</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>42</v>
       </c>
@@ -19721,7 +19805,7 @@
         <v>45564.425057429711</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>43</v>
       </c>
@@ -19742,7 +19826,7 @@
         <v>45750.541367953127</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>44</v>
       </c>
@@ -19763,7 +19847,7 @@
         <v>45937.417904925125</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>45</v>
       </c>
@@ -19784,7 +19868,7 @@
         <v>46125.057773631052</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>46</v>
       </c>
@@ -19805,7 +19889,7 @@
         <v>46313.464092040376</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>47</v>
       </c>
@@ -19826,7 +19910,7 @@
         <v>46502.639990858486</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>48</v>
       </c>
@@ -19847,7 +19931,7 @@
         <v>46692.588613578708</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>49</v>
       </c>
@@ -19868,7 +19952,7 @@
         <v>46883.313116534548</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>50</v>
       </c>
@@ -19889,7 +19973,7 @@
         <v>47074.816668952153</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>51</v>
       </c>
@@ -19910,7 +19994,7 @@
         <v>47267.102453002954</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>52</v>
       </c>
@@ -19931,7 +20015,7 @@
         <v>47460.173663856542</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>53</v>
       </c>
@@ -19952,7 +20036,7 @@
         <v>47654.033509733767</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>54</v>
       </c>
@@ -19973,7 +20057,7 @@
         <v>47848.685211960059</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>55</v>
       </c>
@@ -19994,7 +20078,7 @@
         <v>48044.132005018946</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>56</v>
       </c>
@@ -20015,7 +20099,7 @@
         <v>48240.377136605792</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>57</v>
       </c>
@@ -20036,7 +20120,7 @@
         <v>48437.423867681777</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>58</v>
       </c>
@@ -20057,7 +20141,7 @@
         <v>48635.275472528083</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>59</v>
       </c>
@@ -20078,7 +20162,7 @@
         <v>48833.935238800303</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>60</v>
       </c>
@@ -20099,7 +20183,7 @@
         <v>49033.406467583052</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>61</v>
       </c>
@@ -20120,7 +20204,7 @@
         <v>49233.692473444855</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>62</v>
       </c>
@@ -20141,7 +20225,7 @@
         <v>49434.796584493175</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>63</v>
       </c>
@@ -20162,7 +20246,7 @@
         <v>49636.722142429768</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>64</v>
       </c>
@@ -20183,7 +20267,7 @@
         <v>49839.472502606186</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>65</v>
       </c>
@@ -20204,7 +20288,7 @@
         <v>50043.051034079523</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>66</v>
       </c>
@@ -20225,7 +20309,7 @@
         <v>50247.46111966842</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>67</v>
       </c>
@@ -20246,7 +20330,7 @@
         <v>50452.706156009262</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>68</v>
       </c>
@@ -20267,7 +20351,7 @@
         <v>50658.789553612616</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>69</v>
       </c>
@@ -20288,7 +20372,7 @@
         <v>50865.714736919923</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>70</v>
       </c>
@@ -20309,7 +20393,7 @@
         <v>51073.485144360384</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>71</v>
       </c>
@@ -20330,7 +20414,7 @@
         <v>51282.10422840809</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>72</v>
       </c>
@@ -20351,7 +20435,7 @@
         <v>51491.575455639402</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>73</v>
       </c>
@@ -20372,7 +20456,7 @@
         <v>51701.902306790551</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>74</v>
       </c>
@@ -20393,7 +20477,7 @@
         <v>51913.088276815492</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>75</v>
       </c>
@@ -20414,7 +20498,7 @@
         <v>52125.136874943957</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>76</v>
       </c>
@@ -20435,7 +20519,7 @@
         <v>52338.051624739768</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>77</v>
       </c>
@@ -20456,7 +20540,7 @@
         <v>52551.836064159412</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>78</v>
       </c>
@@ -20477,7 +20561,7 @@
         <v>52766.493745610787</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>79</v>
       </c>
@@ -20498,7 +20582,7 @@
         <v>52982.028236012287</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>80</v>
       </c>
@@ -20529,31 +20613,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A2734E-2BA6-48B0-B7DC-6FB6DAD13E7F}">
   <dimension ref="A1:N82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="3" width="18.140625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="16" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="16" customWidth="1"/>
-    <col min="9" max="9" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="42.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" customWidth="1"/>
-    <col min="14" max="14" width="17.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.68359375" customWidth="1"/>
+    <col min="2" max="3" width="18.15625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9.578125" customWidth="1"/>
+    <col min="6" max="6" width="11.83984375" style="16" customWidth="1"/>
+    <col min="7" max="7" width="11.578125" style="16" customWidth="1"/>
+    <col min="9" max="9" width="9.15625" customWidth="1"/>
+    <col min="12" max="12" width="42.26171875" customWidth="1"/>
+    <col min="13" max="13" width="14.83984375" customWidth="1"/>
+    <col min="14" max="14" width="17.68359375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2">
         <v>0</v>
       </c>
@@ -20564,90 +20648,90 @@
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" s="10">
-        <f>B2*$F$6+C2*$G$6</f>
+        <f t="shared" ref="B3:B34" si="0">B2*$F$6+C2*$G$6</f>
         <v>5.4969548399999999</v>
       </c>
       <c r="C3" s="10">
-        <f>B2*$F$7+C2*$G$7</f>
+        <f t="shared" ref="C3:C34" si="1">B2*$F$7+C2*$G$7</f>
         <v>21.06</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M3" s="4">
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" s="10">
-        <f>B3*$F$6+C3*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.5502261435881728</v>
       </c>
       <c r="C4" s="10">
-        <f>B3*$F$7+C3*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.089233807199999</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M4" s="31">
         <v>0.85</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" s="10">
-        <f>B4*$F$6+C4*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.5637284622116727</v>
       </c>
       <c r="C5" s="10">
-        <f>B4*$F$7+C4*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.14497989940114</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M5" s="30">
         <v>0.8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" s="10">
-        <f>B5*$F$6+C5*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.5782868266263659</v>
       </c>
       <c r="C6" s="10">
-        <f>B5*$F$7+C5*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.200195422573739</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F6" s="18">
         <f>(1-M24)*M27*M5*M7*M8*M23*M10*M11</f>
@@ -20658,22 +20742,22 @@
         <v>0.23038587000000002</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M6" s="6">
         <v>0.99</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" s="10">
-        <f>B6*$F$6+C6*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.5928571090703763</v>
       </c>
       <c r="C7" s="10">
-        <f>B6*$F$7+C6*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.255572468630969</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -20694,16 +20778,16 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" s="10">
-        <f>B7*$F$6+C7*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.6074661180986709</v>
       </c>
       <c r="C8" s="10">
-        <f>B7*$F$7+C7*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.311093721597139</v>
       </c>
       <c r="L8" s="5" t="s">
@@ -20713,19 +20797,19 @@
         <v>0.5</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" s="10">
-        <f>B8*$F$6+C8*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.622113269950952</v>
       </c>
       <c r="C9" s="10">
-        <f>B8*$F$7+C8*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.366760011854797</v>
       </c>
       <c r="L9" s="5" t="s">
@@ -20738,54 +20822,54 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" s="10">
-        <f>B9*$F$6+C9*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.6367986817782656</v>
       </c>
       <c r="C10" s="10">
-        <f>B9*$F$7+C9*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.422571706648128</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M10" s="6">
         <v>0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" s="10">
-        <f>B10*$F$6+C10*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.6515224530706405</v>
       </c>
       <c r="C11" s="10">
-        <f>B10*$F$7+C10*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.478529186082302</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M11" s="6">
         <v>0.4</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" s="10">
-        <f>B11*$F$6+C11*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.6662846840375432</v>
       </c>
       <c r="C12" s="10">
-        <f>B11*$F$7+C11*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.53463283095093</v>
       </c>
       <c r="L12" s="7" t="s">
@@ -20795,79 +20879,79 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" s="10">
-        <f>B12*$F$6+C12*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.6810854751384436</v>
       </c>
       <c r="C13" s="10">
-        <f>B12*$F$7+C12*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.590883023050065</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" s="32"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" s="10">
-        <f>B13*$F$6+C13*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.6959249270955183</v>
       </c>
       <c r="C14" s="10">
-        <f>B13*$F$7+C13*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.647280145172854</v>
       </c>
       <c r="F14" s="17"/>
       <c r="G14" s="17"/>
       <c r="L14" s="11"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" s="10">
-        <f>B14*$F$6+C14*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.7108031408940318</v>
       </c>
       <c r="C15" s="10">
-        <f>B14*$F$7+C14*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.703824581112325</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
       <c r="L15" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>35</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" s="10">
-        <f>B15*$F$6+C15*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.7257202177830306</v>
       </c>
       <c r="C16" s="10">
-        <f>B15*$F$7+C15*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.760516715664014</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
       <c r="L16" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M16" s="14">
         <v>0</v>
@@ -20876,20 +20960,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" s="10">
-        <f>B16*$F$6+C16*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.7406762592760296</v>
       </c>
       <c r="C17" s="10">
-        <f>B16*$F$7+C16*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.81735693462857</v>
       </c>
       <c r="L17" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M17" s="12">
         <v>0.2</v>
@@ -20898,20 +20982,20 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" s="10">
-        <f>B17*$F$6+C17*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.7556713671517068</v>
       </c>
       <c r="C18" s="10">
-        <f>B17*$F$7+C17*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.874345624814381</v>
       </c>
       <c r="L18" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M18" s="12">
         <v>0.75</v>
@@ -20920,20 +21004,20 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" s="10">
-        <f>B18*$F$6+C18*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.7707056434545958</v>
       </c>
       <c r="C19" s="10">
-        <f>B18*$F$7+C18*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.931483174040213</v>
       </c>
       <c r="L19" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M19" s="15">
         <v>0.95</v>
@@ -20942,867 +21026,867 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" s="10">
-        <f>B19*$F$6+C19*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.7857791904957754</v>
       </c>
       <c r="C20" s="10">
-        <f>B19*$F$7+C19*$G$7</f>
+        <f t="shared" si="1"/>
         <v>21.988769971137845</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" s="10">
-        <f>B20*$F$6+C20*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.8008921108535727</v>
       </c>
       <c r="C21" s="10">
-        <f>B20*$F$7+C20*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.046206405954717</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" s="10">
-        <f>B21*$F$6+C21*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.8160445073742544</v>
       </c>
       <c r="C22" s="10">
-        <f>B21*$F$7+C21*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.103792869356582</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" s="10">
-        <f>B22*$F$6+C22*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.8312364831727335</v>
       </c>
       <c r="C23" s="10">
-        <f>B22*$F$7+C22*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.161529753230162</v>
       </c>
       <c r="L23" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M23" s="33">
         <f>(1-N16)*N9+N16*N19</f>
         <v>0.39</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" s="10">
-        <f>B23*$F$6+C23*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.8464681416332631</v>
       </c>
       <c r="C24" s="10">
-        <f>B23*$F$7+C23*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.219417450485821</v>
       </c>
       <c r="L24" s="20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M24" s="30">
         <f>(N16*N17)^0.98</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" s="10">
-        <f>B24*$F$6+C24*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.8617395864101471</v>
       </c>
       <c r="C25" s="10">
-        <f>B24*$F$7+C24*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.277456355060242</v>
       </c>
       <c r="L25" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M25" s="30">
         <f>M5*M24</f>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" s="10">
-        <f>B25*$F$6+C25*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.8770509214284425</v>
       </c>
       <c r="C26" s="10">
-        <f>B25*$F$7+C25*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.335646861919088</v>
       </c>
       <c r="L26" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M26" s="30">
         <f>M6*M24</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" s="10">
-        <f>B26*$F$6+C26*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.8924022508846665</v>
       </c>
       <c r="C27" s="10">
-        <f>B26*$F$7+C26*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.393989367059721</v>
       </c>
       <c r="L27" s="20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M27" s="30">
         <f>(1-M25)*M3+M25*(1-N18)</f>
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="14.7" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" s="10">
-        <f>B27*$F$6+C27*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.9077936792475061</v>
       </c>
       <c r="C28" s="10">
-        <f>B27*$F$7+C27*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.452484267513867</v>
       </c>
       <c r="L28" s="21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M28" s="34">
         <f>(1-M26)*M4+M26*(1-N18)</f>
         <v>0.85</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
         <v>27</v>
       </c>
       <c r="B29" s="10">
-        <f>B28*$F$6+C28*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.9232253112585287</v>
       </c>
       <c r="C29" s="10">
-        <f>B28*$F$7+C28*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.511131961350337</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
         <v>28</v>
       </c>
       <c r="B30" s="10">
-        <f>B29*$F$6+C29*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.9386972519328953</v>
       </c>
       <c r="C30" s="10">
-        <f>B29*$F$7+C29*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.56993284767773</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
         <v>29</v>
       </c>
       <c r="B31" s="10">
-        <f>B30*$F$6+C30*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.9542096065600756</v>
       </c>
       <c r="C31" s="10">
-        <f>B30*$F$7+C30*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.628887326647149</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
         <v>30</v>
       </c>
       <c r="B32" s="10">
-        <f>B31*$F$6+C31*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.9697624807045617</v>
       </c>
       <c r="C32" s="10">
-        <f>B31*$F$7+C31*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.687995799454921</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
         <v>31</v>
       </c>
       <c r="B33" s="10">
-        <f>B32*$F$6+C32*$G$6</f>
+        <f t="shared" si="0"/>
         <v>5.9853559802065925</v>
       </c>
       <c r="C33" s="10">
-        <f>B32*$F$7+C32*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.747258668345328</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
         <v>32</v>
       </c>
       <c r="B34" s="10">
-        <f>B33*$F$6+C33*$G$6</f>
+        <f t="shared" si="0"/>
         <v>6.0009902111828657</v>
       </c>
       <c r="C34" s="10">
-        <f>B33*$F$7+C33*$G$7</f>
+        <f t="shared" si="1"/>
         <v>22.806676336613354</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
         <v>33</v>
       </c>
       <c r="B35" s="10">
-        <f>B34*$F$6+C34*$G$6</f>
+        <f t="shared" ref="B35:B66" si="2">B34*$F$6+C34*$G$6</f>
         <v>6.0166652800272686</v>
       </c>
       <c r="C35" s="10">
-        <f>B34*$F$7+C34*$G$7</f>
+        <f t="shared" ref="C35:C66" si="3">B34*$F$7+C34*$G$7</f>
         <v>22.866249208607414</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
         <v>34</v>
       </c>
       <c r="B36" s="10">
-        <f>B35*$F$6+C35*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.0323812934115919</v>
       </c>
       <c r="C36" s="10">
-        <f>B35*$F$7+C35*$G$7</f>
+        <f t="shared" si="3"/>
         <v>22.925977689732118</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
         <v>35</v>
       </c>
       <c r="B37" s="10">
-        <f>B36*$F$6+C36*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.0481383582862689</v>
       </c>
       <c r="C37" s="10">
-        <f>B36*$F$7+C36*$G$7</f>
+        <f t="shared" si="3"/>
         <v>22.985862186451023</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
         <v>36</v>
       </c>
       <c r="B38" s="10">
-        <f>B37*$F$6+C37*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.0639365818810909</v>
       </c>
       <c r="C38" s="10">
-        <f>B37*$F$7+C37*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.045903106289401</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
         <v>37</v>
       </c>
       <c r="B39" s="10">
-        <f>B38*$F$6+C38*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.0797760717059433</v>
       </c>
       <c r="C39" s="10">
-        <f>B38*$F$7+C38*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.106100857837021</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
         <v>38</v>
       </c>
       <c r="B40" s="10">
-        <f>B39*$F$6+C39*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.0956569355515358</v>
       </c>
       <c r="C40" s="10">
-        <f>B39*$F$7+C39*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.166455850750914</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
         <v>39</v>
       </c>
       <c r="B41" s="10">
-        <f>B40*$F$6+C40*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.1115792814901395</v>
       </c>
       <c r="C41" s="10">
-        <f>B40*$F$7+C40*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.226968495758168</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
         <v>40</v>
       </c>
       <c r="B42" s="10">
-        <f>B41*$F$6+C41*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.1275432178763136</v>
       </c>
       <c r="C42" s="10">
-        <f>B41*$F$7+C41*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.287639204658724</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
         <v>41</v>
       </c>
       <c r="B43" s="10">
-        <f>B42*$F$6+C42*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.1435488533476512</v>
       </c>
       <c r="C43" s="10">
-        <f>B42*$F$7+C42*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.348468390328179</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
         <v>42</v>
       </c>
       <c r="B44" s="10">
-        <f>B43*$F$6+C43*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.1595962968255149</v>
       </c>
       <c r="C44" s="10">
-        <f>B43*$F$7+C43*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.409456466720588</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
         <v>43</v>
       </c>
       <c r="B45" s="10">
-        <f>B44*$F$6+C44*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.1756856575157775</v>
       </c>
       <c r="C45" s="10">
-        <f>B44*$F$7+C44*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.470603848871299</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
         <v>44</v>
       </c>
       <c r="B46" s="10">
-        <f>B45*$F$6+C45*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.1918170449095697</v>
       </c>
       <c r="C46" s="10">
-        <f>B45*$F$7+C45*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.531910952899757</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
         <v>45</v>
       </c>
       <c r="B47" s="10">
-        <f>B46*$F$6+C46*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.2079905687840196</v>
       </c>
       <c r="C47" s="10">
-        <f>B46*$F$7+C46*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.593378196012342</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
         <v>46</v>
       </c>
       <c r="B48" s="10">
-        <f>B47*$F$6+C47*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.2242063392029978</v>
       </c>
       <c r="C48" s="10">
-        <f>B47*$F$7+C47*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.655005996505221</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
         <v>47</v>
       </c>
       <c r="B49" s="10">
-        <f>B48*$F$6+C48*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.2404644665178797</v>
       </c>
       <c r="C49" s="10">
-        <f>B48*$F$7+C48*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.716794773767177</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
         <v>48</v>
       </c>
       <c r="B50" s="10">
-        <f>B49*$F$6+C49*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.2567650613682799</v>
       </c>
       <c r="C50" s="10">
-        <f>B49*$F$7+C49*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.778744948282469</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51">
         <v>49</v>
       </c>
       <c r="B51" s="10">
-        <f>B50*$F$6+C50*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.273108234682816</v>
       </c>
       <c r="C51" s="10">
-        <f>B50*$F$7+C50*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.8408569416337</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52">
         <v>50</v>
       </c>
       <c r="B52" s="10">
-        <f>B51*$F$6+C51*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.2894940976798575</v>
       </c>
       <c r="C52" s="10">
-        <f>B51*$F$7+C51*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.903131176504679</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53">
         <v>51</v>
       </c>
       <c r="B53" s="10">
-        <f>B52*$F$6+C52*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.30592276186829</v>
       </c>
       <c r="C53" s="10">
-        <f>B52*$F$7+C52*$G$7</f>
+        <f t="shared" si="3"/>
         <v>23.965568076683294</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A54">
         <v>52</v>
       </c>
       <c r="B54" s="10">
-        <f>B53*$F$6+C53*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.3223943390482633</v>
       </c>
       <c r="C54" s="10">
-        <f>B53*$F$7+C53*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.028168067064406</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A55">
         <v>53</v>
       </c>
       <c r="B55" s="10">
-        <f>B54*$F$6+C54*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.3389089413119617</v>
       </c>
       <c r="C55" s="10">
-        <f>B54*$F$7+C54*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.090931573652739</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A56">
         <v>54</v>
       </c>
       <c r="B56" s="10">
-        <f>B55*$F$6+C55*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.3554666810443639</v>
       </c>
       <c r="C56" s="10">
-        <f>B55*$F$7+C55*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.153859023565765</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A57">
         <v>55</v>
       </c>
       <c r="B57" s="10">
-        <f>B56*$F$6+C56*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.3720676709240056</v>
       </c>
       <c r="C57" s="10">
-        <f>B56*$F$7+C56*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.216950845036632</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A58">
         <v>56</v>
       </c>
       <c r="B58" s="10">
-        <f>B57*$F$6+C57*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.3887120239237465</v>
       </c>
       <c r="C58" s="10">
-        <f>B57*$F$7+C57*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.28020746741706</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A59">
         <v>57</v>
       </c>
       <c r="B59" s="10">
-        <f>B58*$F$6+C58*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.4053998533115433</v>
       </c>
       <c r="C59" s="10">
-        <f>B58*$F$7+C58*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.343629321180273</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A60">
         <v>58</v>
       </c>
       <c r="B60" s="10">
-        <f>B59*$F$6+C59*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.4221312726512174</v>
       </c>
       <c r="C60" s="10">
-        <f>B59*$F$7+C59*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.407216837923926</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A61">
         <v>59</v>
       </c>
       <c r="B61" s="10">
-        <f>B60*$F$6+C60*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.438906395803226</v>
       </c>
       <c r="C61" s="10">
-        <f>B60*$F$7+C60*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.470970450373045</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A62">
         <v>60</v>
       </c>
       <c r="B62" s="10">
-        <f>B61*$F$6+C61*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.4557253369254415</v>
       </c>
       <c r="C62" s="10">
-        <f>B61*$F$7+C61*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.534890592382958</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A63">
         <v>61</v>
       </c>
       <c r="B63" s="10">
-        <f>B62*$F$6+C62*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.4725882104739236</v>
       </c>
       <c r="C63" s="10">
-        <f>B62*$F$7+C62*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.598977698942271</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A64">
         <v>62</v>
       </c>
       <c r="B64" s="10">
-        <f>B63*$F$6+C63*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.4894951312037019</v>
       </c>
       <c r="C64" s="10">
-        <f>B63*$F$7+C63*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.663232206175806</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A65">
         <v>63</v>
       </c>
       <c r="B65" s="10">
-        <f>B64*$F$6+C64*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.5064462141695536</v>
       </c>
       <c r="C65" s="10">
-        <f>B64*$F$7+C64*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.72765455134758</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A66">
         <v>64</v>
       </c>
       <c r="B66" s="10">
-        <f>B65*$F$6+C65*$G$6</f>
+        <f t="shared" si="2"/>
         <v>6.5234415747267906</v>
       </c>
       <c r="C66" s="10">
-        <f>B65*$F$7+C65*$G$7</f>
+        <f t="shared" si="3"/>
         <v>24.792245172863783</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A67">
         <v>65</v>
       </c>
       <c r="B67" s="10">
-        <f>B66*$F$6+C66*$G$6</f>
+        <f t="shared" ref="B67:B82" si="4">B66*$F$6+C66*$G$6</f>
         <v>6.5404813285320405</v>
       </c>
       <c r="C67" s="10">
-        <f>B66*$F$7+C66*$G$7</f>
+        <f t="shared" ref="C67:C82" si="5">B66*$F$7+C66*$G$7</f>
         <v>24.857004510275754</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A68">
         <v>66</v>
       </c>
       <c r="B68" s="10">
-        <f>B67*$F$6+C67*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.5575655915440372</v>
       </c>
       <c r="C68" s="10">
-        <f>B67*$F$7+C67*$G$7</f>
+        <f t="shared" si="5"/>
         <v>24.921933004282973</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A69">
         <v>67</v>
       </c>
       <c r="B69" s="10">
-        <f>B68*$F$6+C68*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.5746944800244052</v>
       </c>
       <c r="C69" s="10">
-        <f>B68*$F$7+C68*$G$7</f>
+        <f t="shared" si="5"/>
         <v>24.987031096736068</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A70">
         <v>68</v>
       </c>
       <c r="B70" s="10">
-        <f>B69*$F$6+C69*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.5918681105384556</v>
       </c>
       <c r="C70" s="10">
-        <f>B69*$F$7+C69*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.052299230639814</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A71">
         <v>69</v>
       </c>
       <c r="B71" s="10">
-        <f>B70*$F$6+C70*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.6090865999559778</v>
       </c>
       <c r="C71" s="10">
-        <f>B70*$F$7+C70*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.117737850156146</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A72">
         <v>70</v>
       </c>
       <c r="B72" s="10">
-        <f>B71*$F$6+C71*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.6263500654520335</v>
       </c>
       <c r="C72" s="10">
-        <f>B71*$F$7+C71*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.18334740060719</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A73">
         <v>71</v>
       </c>
       <c r="B73" s="10">
-        <f>B72*$F$6+C72*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.6436586245077542</v>
       </c>
       <c r="C73" s="10">
-        <f>B72*$F$7+C72*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.249128328478292</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A74">
         <v>72</v>
       </c>
       <c r="B74" s="10">
-        <f>B73*$F$6+C73*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.6610123949111459</v>
       </c>
       <c r="C74" s="10">
-        <f>B73*$F$7+C73*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.315081081421045</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A75">
         <v>73</v>
       </c>
       <c r="B75" s="10">
-        <f>B74*$F$6+C74*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.6784114947578797</v>
       </c>
       <c r="C75" s="10">
-        <f>B74*$F$7+C74*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.38120610825635</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A76">
         <v>74</v>
       </c>
       <c r="B76" s="10">
-        <f>B75*$F$6+C75*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.6958560424521067</v>
       </c>
       <c r="C76" s="10">
-        <f>B75*$F$7+C75*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.447503858977466</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A77">
         <v>75</v>
       </c>
       <c r="B77" s="10">
-        <f>B76*$F$6+C76*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.7133461567072592</v>
       </c>
       <c r="C77" s="10">
-        <f>B76*$F$7+C76*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.513974784753067</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A78">
         <v>76</v>
       </c>
       <c r="B78" s="10">
-        <f>B77*$F$6+C77*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.7308819565468561</v>
       </c>
       <c r="C78" s="10">
-        <f>B77*$F$7+C77*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.580619337930319</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A79">
         <v>77</v>
       </c>
       <c r="B79" s="10">
-        <f>B78*$F$6+C78*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.7484635613053179</v>
       </c>
       <c r="C79" s="10">
-        <f>B78*$F$7+C78*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.647437972037949</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A80">
         <v>78</v>
       </c>
       <c r="B80" s="10">
-        <f>B79*$F$6+C79*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.7660910906287741</v>
       </c>
       <c r="C80" s="10">
-        <f>B79*$F$7+C79*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.714431141789337</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A81">
         <v>79</v>
       </c>
       <c r="B81" s="10">
-        <f>B80*$F$6+C80*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.7837646644758784</v>
       </c>
       <c r="C81" s="10">
-        <f>B80*$F$7+C80*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.781599303085628</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A82">
         <v>80</v>
       </c>
       <c r="B82" s="10">
-        <f>B81*$F$6+C81*$G$6</f>
+        <f t="shared" si="4"/>
         <v>6.8014844031186321</v>
       </c>
       <c r="C82" s="10">
-        <f>B81*$F$7+C81*$G$7</f>
+        <f t="shared" si="5"/>
         <v>25.848942913018792</v>
       </c>
     </row>
